--- a/research/traditional_assets/database/data/singapore/singapore_retail_building_supply.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_retail_building_supply.xlsx
@@ -1388,7 +1388,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1525,22 +1525,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08706475818401804</v>
+        <v>0.08695409809510522</v>
       </c>
       <c r="C2">
-        <v>57.08785763585729</v>
+        <v>56.5401656851079</v>
       </c>
       <c r="D2">
-        <v>36.18785763585729</v>
+        <v>36.2114656851079</v>
       </c>
       <c r="E2">
-        <v>-2.33</v>
+        <v>-1.7587</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.5712999999999999</v>
       </c>
       <c r="G2">
         <v>20.9</v>
@@ -1561,28 +1561,28 @@
         <v>8.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.02873638999999999</v>
       </c>
       <c r="N2">
-        <v>8.5</v>
+        <v>8.471263609999999</v>
       </c>
       <c r="O2">
-        <v>1.445</v>
+        <v>1.4401148137</v>
       </c>
       <c r="P2">
-        <v>7.055</v>
+        <v>7.031148796299999</v>
       </c>
       <c r="Q2">
-        <v>7.615</v>
+        <v>7.5911487963</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08706475818401804</v>
+        <v>0.08741071524758103</v>
       </c>
       <c r="T2">
-        <v>0.952996724804112</v>
+        <v>0.960986495325197</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>295.7921993681183</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1607,22 +1607,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08695409809510522</v>
+        <v>0.08684343800619239</v>
       </c>
       <c r="C3">
-        <v>56.5401656851079</v>
+        <v>55.99250455706302</v>
       </c>
       <c r="D3">
-        <v>36.2114656851079</v>
+        <v>36.23510455706302</v>
       </c>
       <c r="E3">
-        <v>-1.7587</v>
+        <v>-1.1874</v>
       </c>
       <c r="F3">
-        <v>0.5712999999999999</v>
+        <v>1.1426</v>
       </c>
       <c r="G3">
         <v>20.9</v>
@@ -1643,28 +1643,28 @@
         <v>8.5</v>
       </c>
       <c r="M3">
-        <v>0.02873638999999999</v>
+        <v>0.05747277999999999</v>
       </c>
       <c r="N3">
-        <v>8.471263609999999</v>
+        <v>8.442527220000001</v>
       </c>
       <c r="O3">
-        <v>1.4401148137</v>
+        <v>1.4352296274</v>
       </c>
       <c r="P3">
-        <v>7.031148796299999</v>
+        <v>7.007297592600001</v>
       </c>
       <c r="Q3">
-        <v>7.5911487963</v>
+        <v>7.567297592600001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08741071524758103</v>
+        <v>0.08776373265937999</v>
       </c>
       <c r="T3">
-        <v>0.960986495325197</v>
+        <v>0.9691393223875286</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>295.7921993681183</v>
+        <v>147.8960996840592</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1689,22 +1689,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08684343800619239</v>
+        <v>0.08673277791727957</v>
       </c>
       <c r="C4">
-        <v>55.99250455706302</v>
+        <v>55.44487431212534</v>
       </c>
       <c r="D4">
-        <v>36.23510455706302</v>
+        <v>36.25877431212534</v>
       </c>
       <c r="E4">
-        <v>-1.1874</v>
+        <v>-0.6161000000000003</v>
       </c>
       <c r="F4">
-        <v>1.1426</v>
+        <v>1.7139</v>
       </c>
       <c r="G4">
         <v>20.9</v>
@@ -1725,28 +1725,28 @@
         <v>8.5</v>
       </c>
       <c r="M4">
-        <v>0.05747277999999999</v>
+        <v>0.08620916999999999</v>
       </c>
       <c r="N4">
-        <v>8.442527220000001</v>
+        <v>8.41379083</v>
       </c>
       <c r="O4">
-        <v>1.4352296274</v>
+        <v>1.4303444411</v>
       </c>
       <c r="P4">
-        <v>7.007297592600001</v>
+        <v>6.9834463889</v>
       </c>
       <c r="Q4">
-        <v>7.567297592600001</v>
+        <v>7.543446388900001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08776373265937999</v>
+        <v>0.08812402878070058</v>
       </c>
       <c r="T4">
-        <v>0.9691393223875286</v>
+        <v>0.9774602489769186</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>147.8960996840592</v>
+        <v>98.59739978937277</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1771,22 +1771,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08673277791727957</v>
+        <v>0.08662211782836672</v>
       </c>
       <c r="C5">
-        <v>55.44487431212534</v>
+        <v>54.89727501085547</v>
       </c>
       <c r="D5">
-        <v>36.25877431212534</v>
+        <v>36.28247501085547</v>
       </c>
       <c r="E5">
-        <v>-0.6161000000000003</v>
+        <v>-0.0448000000000004</v>
       </c>
       <c r="F5">
-        <v>1.7139</v>
+        <v>2.2852</v>
       </c>
       <c r="G5">
         <v>20.9</v>
@@ -1807,28 +1807,28 @@
         <v>8.5</v>
       </c>
       <c r="M5">
-        <v>0.08620916999999999</v>
+        <v>0.11494556</v>
       </c>
       <c r="N5">
-        <v>8.41379083</v>
+        <v>8.385054439999999</v>
       </c>
       <c r="O5">
-        <v>1.4303444411</v>
+        <v>1.4254592548</v>
       </c>
       <c r="P5">
-        <v>6.9834463889</v>
+        <v>6.9595951852</v>
       </c>
       <c r="Q5">
-        <v>7.543446388900001</v>
+        <v>7.5195951852</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08812402878070058</v>
+        <v>0.08849183107121535</v>
       </c>
       <c r="T5">
-        <v>0.9774602489769186</v>
+        <v>0.9859545282035876</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>98.59739978937277</v>
+        <v>73.94804984202958</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1853,22 +1853,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08662211782836672</v>
+        <v>0.0865114577394539</v>
       </c>
       <c r="C6">
-        <v>54.89727501085547</v>
+        <v>54.34970671397246</v>
       </c>
       <c r="D6">
-        <v>36.28247501085547</v>
+        <v>36.30620671397246</v>
       </c>
       <c r="E6">
-        <v>-0.0448000000000004</v>
+        <v>0.5265</v>
       </c>
       <c r="F6">
-        <v>2.2852</v>
+        <v>2.8565</v>
       </c>
       <c r="G6">
         <v>20.9</v>
@@ -1889,28 +1889,28 @@
         <v>8.5</v>
       </c>
       <c r="M6">
-        <v>0.11494556</v>
+        <v>0.14368195</v>
       </c>
       <c r="N6">
-        <v>8.385054439999999</v>
+        <v>8.35631805</v>
       </c>
       <c r="O6">
-        <v>1.4254592548</v>
+        <v>1.4205740685</v>
       </c>
       <c r="P6">
-        <v>6.9595951852</v>
+        <v>6.9357439815</v>
       </c>
       <c r="Q6">
-        <v>7.5195951852</v>
+        <v>7.4957439815</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08849183107121535</v>
+        <v>0.08886737656784621</v>
       </c>
       <c r="T6">
-        <v>0.9859545282035876</v>
+        <v>0.9946276343613443</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>73.94804984202958</v>
+        <v>59.15843987362366</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1935,22 +1935,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0865114577394539</v>
+        <v>0.08640079765054105</v>
       </c>
       <c r="C7">
-        <v>54.34970671397246</v>
+        <v>53.80216948235437</v>
       </c>
       <c r="D7">
-        <v>36.30620671397246</v>
+        <v>36.32996948235436</v>
       </c>
       <c r="E7">
-        <v>0.5265</v>
+        <v>1.0978</v>
       </c>
       <c r="F7">
-        <v>2.8565</v>
+        <v>3.4278</v>
       </c>
       <c r="G7">
         <v>20.9</v>
@@ -1971,28 +1971,28 @@
         <v>8.5</v>
       </c>
       <c r="M7">
-        <v>0.14368195</v>
+        <v>0.17241834</v>
       </c>
       <c r="N7">
-        <v>8.35631805</v>
+        <v>8.32758166</v>
       </c>
       <c r="O7">
-        <v>1.4205740685</v>
+        <v>1.4156888822</v>
       </c>
       <c r="P7">
-        <v>6.9357439815</v>
+        <v>6.9118927778</v>
       </c>
       <c r="Q7">
-        <v>7.4957439815</v>
+        <v>7.471892777800001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08886737656784621</v>
+        <v>0.08925091239419262</v>
       </c>
       <c r="T7">
-        <v>0.9946276343613443</v>
+        <v>1.00348527469267</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>59.15843987362366</v>
+        <v>49.29869989468639</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2017,22 +2017,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08640079765054105</v>
+        <v>0.08629013756162825</v>
       </c>
       <c r="C8">
-        <v>53.80216948235437</v>
+        <v>53.25466337703865</v>
       </c>
       <c r="D8">
-        <v>36.32996948235436</v>
+        <v>36.35376337703865</v>
       </c>
       <c r="E8">
-        <v>1.097799999999999</v>
+        <v>1.669099999999999</v>
       </c>
       <c r="F8">
-        <v>3.4278</v>
+        <v>3.999099999999999</v>
       </c>
       <c r="G8">
         <v>20.9</v>
@@ -2053,28 +2053,28 @@
         <v>8.5</v>
       </c>
       <c r="M8">
-        <v>0.17241834</v>
+        <v>0.2011547299999999</v>
       </c>
       <c r="N8">
-        <v>8.32758166</v>
+        <v>8.298845269999999</v>
       </c>
       <c r="O8">
-        <v>1.4156888822</v>
+        <v>1.4108036959</v>
       </c>
       <c r="P8">
-        <v>6.9118927778</v>
+        <v>6.888041574099999</v>
       </c>
       <c r="Q8">
-        <v>7.471892777800001</v>
+        <v>7.448041574099999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08925091239419262</v>
+        <v>0.08964269630282606</v>
       </c>
       <c r="T8">
-        <v>1.00348527469267</v>
+        <v>1.012533401912842</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>49.29869989468639</v>
+        <v>42.25602848115976</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2099,22 +2099,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08629013756162823</v>
+        <v>0.08617947747271541</v>
       </c>
       <c r="C9">
-        <v>53.25466337703865</v>
+        <v>52.70718845922288</v>
       </c>
       <c r="D9">
-        <v>36.35376337703865</v>
+        <v>36.37758845922288</v>
       </c>
       <c r="E9">
-        <v>1.6691</v>
+        <v>2.240399999999999</v>
       </c>
       <c r="F9">
-        <v>3.9991</v>
+        <v>4.570399999999999</v>
       </c>
       <c r="G9">
         <v>20.9</v>
@@ -2135,28 +2135,28 @@
         <v>8.5</v>
       </c>
       <c r="M9">
-        <v>0.20115473</v>
+        <v>0.2298911199999999</v>
       </c>
       <c r="N9">
-        <v>8.298845269999999</v>
+        <v>8.27010888</v>
       </c>
       <c r="O9">
-        <v>1.4108036959</v>
+        <v>1.4059185096</v>
       </c>
       <c r="P9">
-        <v>6.888041574099999</v>
+        <v>6.8641903704</v>
       </c>
       <c r="Q9">
-        <v>7.448041574099999</v>
+        <v>7.424190370400001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08964269630282606</v>
+        <v>0.09004299725295153</v>
       </c>
       <c r="T9">
-        <v>1.012533401912842</v>
+        <v>1.021778227550844</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>42.25602848115975</v>
+        <v>36.9740249210148</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2181,22 +2181,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08617947747271541</v>
+        <v>0.08606881738380258</v>
       </c>
       <c r="C10">
-        <v>52.70718845922288</v>
+        <v>52.15974479026509</v>
       </c>
       <c r="D10">
-        <v>36.37758845922288</v>
+        <v>36.4014447902651</v>
       </c>
       <c r="E10">
-        <v>2.240399999999999</v>
+        <v>2.811699999999999</v>
       </c>
       <c r="F10">
-        <v>4.570399999999999</v>
+        <v>5.141699999999999</v>
       </c>
       <c r="G10">
         <v>20.9</v>
@@ -2217,28 +2217,28 @@
         <v>8.5</v>
       </c>
       <c r="M10">
-        <v>0.2298911199999999</v>
+        <v>0.2586275099999999</v>
       </c>
       <c r="N10">
-        <v>8.27010888</v>
+        <v>8.24137249</v>
       </c>
       <c r="O10">
-        <v>1.4059185096</v>
+        <v>1.4010333233</v>
       </c>
       <c r="P10">
-        <v>6.8641903704</v>
+        <v>6.8403391667</v>
       </c>
       <c r="Q10">
-        <v>7.424190370400001</v>
+        <v>7.4003391667</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09004299725295153</v>
+        <v>0.09045209602615667</v>
       </c>
       <c r="T10">
-        <v>1.021778227550844</v>
+        <v>1.0312262361699</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>36.9740249210148</v>
+        <v>32.86579992979092</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08606881738380258</v>
+        <v>0.08595815729488974</v>
       </c>
       <c r="C11">
-        <v>52.15974479026509</v>
+        <v>51.61233243168439</v>
       </c>
       <c r="D11">
-        <v>36.4014447902651</v>
+        <v>36.42533243168439</v>
       </c>
       <c r="E11">
-        <v>2.811699999999999</v>
+        <v>3.382999999999999</v>
       </c>
       <c r="F11">
-        <v>5.141699999999999</v>
+        <v>5.712999999999999</v>
       </c>
       <c r="G11">
         <v>20.9</v>
@@ -2299,28 +2299,28 @@
         <v>8.5</v>
       </c>
       <c r="M11">
-        <v>0.2586275099999999</v>
+        <v>0.2873638999999999</v>
       </c>
       <c r="N11">
-        <v>8.24137249</v>
+        <v>8.212636099999999</v>
       </c>
       <c r="O11">
-        <v>1.4010333233</v>
+        <v>1.396148137</v>
       </c>
       <c r="P11">
-        <v>6.8403391667</v>
+        <v>6.816487962999999</v>
       </c>
       <c r="Q11">
-        <v>7.4003391667</v>
+        <v>7.376487963</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09045209602615667</v>
+        <v>0.09087028588321083</v>
       </c>
       <c r="T11">
-        <v>1.0312262361699</v>
+        <v>1.040884200536047</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>32.86579992979092</v>
+        <v>29.57921993681183</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2345,22 +2345,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08595815729488974</v>
+        <v>0.08584749720597692</v>
       </c>
       <c r="C12">
-        <v>51.61233243168439</v>
+        <v>51.06495144516148</v>
       </c>
       <c r="D12">
-        <v>36.42533243168439</v>
+        <v>36.44925144516148</v>
       </c>
       <c r="E12">
-        <v>3.383</v>
+        <v>3.954299999999999</v>
       </c>
       <c r="F12">
-        <v>5.713</v>
+        <v>6.284299999999999</v>
       </c>
       <c r="G12">
         <v>20.9</v>
@@ -2381,28 +2381,28 @@
         <v>8.5</v>
       </c>
       <c r="M12">
-        <v>0.2873639</v>
+        <v>0.31610029</v>
       </c>
       <c r="N12">
-        <v>8.212636099999999</v>
+        <v>8.18389971</v>
       </c>
       <c r="O12">
-        <v>1.396148137</v>
+        <v>1.3912629507</v>
       </c>
       <c r="P12">
-        <v>6.816487962999999</v>
+        <v>6.792636759300001</v>
       </c>
       <c r="Q12">
-        <v>7.376487963</v>
+        <v>7.352636759300001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09087028588321083</v>
+        <v>0.0912978732651426</v>
       </c>
       <c r="T12">
-        <v>1.040884200536047</v>
+        <v>1.050759197809298</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>29.57921993681182</v>
+        <v>26.89019994255621</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2427,22 +2427,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08584749720597692</v>
+        <v>0.08573683711706408</v>
       </c>
       <c r="C13">
-        <v>51.06495144516148</v>
+        <v>50.51760189253918</v>
       </c>
       <c r="D13">
-        <v>36.44925144516148</v>
+        <v>36.47320189253918</v>
       </c>
       <c r="E13">
-        <v>3.954299999999999</v>
+        <v>4.525599999999999</v>
       </c>
       <c r="F13">
-        <v>6.284299999999999</v>
+        <v>6.855599999999999</v>
       </c>
       <c r="G13">
         <v>20.9</v>
@@ -2463,28 +2463,28 @@
         <v>8.5</v>
       </c>
       <c r="M13">
-        <v>0.31610029</v>
+        <v>0.34483668</v>
       </c>
       <c r="N13">
-        <v>8.18389971</v>
+        <v>8.15516332</v>
       </c>
       <c r="O13">
-        <v>1.3912629507</v>
+        <v>1.3863777644</v>
       </c>
       <c r="P13">
-        <v>6.792636759300001</v>
+        <v>6.768785555599999</v>
       </c>
       <c r="Q13">
-        <v>7.352636759300001</v>
+        <v>7.3287855556</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0912978732651426</v>
+        <v>0.09173517854211828</v>
       </c>
       <c r="T13">
-        <v>1.050759197809298</v>
+        <v>1.060858626838759</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>26.89019994255621</v>
+        <v>24.64934994734319</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2509,22 +2509,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08573683711706408</v>
+        <v>0.08562617702815126</v>
       </c>
       <c r="C14">
-        <v>50.51760189253918</v>
+        <v>49.97028383582295</v>
       </c>
       <c r="D14">
-        <v>36.47320189253918</v>
+        <v>36.49718383582296</v>
       </c>
       <c r="E14">
-        <v>4.525599999999999</v>
+        <v>5.0969</v>
       </c>
       <c r="F14">
-        <v>6.855599999999999</v>
+        <v>7.4269</v>
       </c>
       <c r="G14">
         <v>20.9</v>
@@ -2545,28 +2545,28 @@
         <v>8.5</v>
       </c>
       <c r="M14">
-        <v>0.34483668</v>
+        <v>0.37357307</v>
       </c>
       <c r="N14">
-        <v>8.15516332</v>
+        <v>8.126426930000001</v>
       </c>
       <c r="O14">
-        <v>1.3863777644</v>
+        <v>1.3814925781</v>
       </c>
       <c r="P14">
-        <v>6.768785555599999</v>
+        <v>6.7449343519</v>
       </c>
       <c r="Q14">
-        <v>7.3287855556</v>
+        <v>7.304934351900001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09173517854211828</v>
+        <v>0.09218253681396696</v>
       </c>
       <c r="T14">
-        <v>1.060858626838759</v>
+        <v>1.071190226650507</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>24.64934994734319</v>
+        <v>22.75324610523987</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2591,22 +2591,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08562617702815126</v>
+        <v>0.08551551693923841</v>
       </c>
       <c r="C15">
-        <v>49.97028383582295</v>
+        <v>49.42299733718149</v>
       </c>
       <c r="D15">
-        <v>36.49718383582296</v>
+        <v>36.52119733718148</v>
       </c>
       <c r="E15">
-        <v>5.0969</v>
+        <v>5.6682</v>
       </c>
       <c r="F15">
-        <v>7.4269</v>
+        <v>7.9982</v>
       </c>
       <c r="G15">
         <v>20.9</v>
@@ -2627,28 +2627,28 @@
         <v>8.5</v>
       </c>
       <c r="M15">
-        <v>0.37357307</v>
+        <v>0.40230946</v>
       </c>
       <c r="N15">
-        <v>8.126426930000001</v>
+        <v>8.09769054</v>
       </c>
       <c r="O15">
-        <v>1.3814925781</v>
+        <v>1.3766073918</v>
       </c>
       <c r="P15">
-        <v>6.7449343519</v>
+        <v>6.7210831482</v>
       </c>
       <c r="Q15">
-        <v>7.304934351900001</v>
+        <v>7.2810831482</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09218253681396696</v>
+        <v>0.0926402987665563</v>
       </c>
       <c r="T15">
-        <v>1.071190226650507</v>
+        <v>1.081762096225319</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>22.75324610523987</v>
+        <v>21.12801424057988</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2673,22 +2673,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08551551693923841</v>
+        <v>0.08540485685032559</v>
       </c>
       <c r="C16">
-        <v>49.42299733718149</v>
+        <v>48.87574245894712</v>
       </c>
       <c r="D16">
-        <v>36.52119733718148</v>
+        <v>36.54524245894711</v>
       </c>
       <c r="E16">
-        <v>5.6682</v>
+        <v>6.239500000000001</v>
       </c>
       <c r="F16">
-        <v>7.9982</v>
+        <v>8.569500000000001</v>
       </c>
       <c r="G16">
         <v>20.9</v>
@@ -2709,28 +2709,28 @@
         <v>8.5</v>
       </c>
       <c r="M16">
-        <v>0.40230946</v>
+        <v>0.4310458500000001</v>
       </c>
       <c r="N16">
-        <v>8.09769054</v>
+        <v>8.06895415</v>
       </c>
       <c r="O16">
-        <v>1.3766073918</v>
+        <v>1.3717222055</v>
       </c>
       <c r="P16">
-        <v>6.7210831482</v>
+        <v>6.697231944499999</v>
       </c>
       <c r="Q16">
-        <v>7.2810831482</v>
+        <v>7.2572319445</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0926402987665563</v>
+        <v>0.09310883158861834</v>
       </c>
       <c r="T16">
-        <v>1.081762096225319</v>
+        <v>1.092582715672479</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>21.12801424057988</v>
+        <v>19.71947995787455</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2755,22 +2755,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08540485685032559</v>
+        <v>0.08529419676141275</v>
       </c>
       <c r="C17">
-        <v>48.87574245894712</v>
+        <v>48.32851926361653</v>
       </c>
       <c r="D17">
-        <v>36.54524245894711</v>
+        <v>36.56931926361653</v>
       </c>
       <c r="E17">
-        <v>6.2395</v>
+        <v>6.810799999999999</v>
       </c>
       <c r="F17">
-        <v>8.5695</v>
+        <v>9.140799999999999</v>
       </c>
       <c r="G17">
         <v>20.9</v>
@@ -2791,28 +2791,28 @@
         <v>8.5</v>
       </c>
       <c r="M17">
-        <v>0.43104585</v>
+        <v>0.4597822399999999</v>
       </c>
       <c r="N17">
-        <v>8.06895415</v>
+        <v>8.040217760000001</v>
       </c>
       <c r="O17">
-        <v>1.3717222055</v>
+        <v>1.3668370192</v>
       </c>
       <c r="P17">
-        <v>6.697231944499999</v>
+        <v>6.673380740800001</v>
       </c>
       <c r="Q17">
-        <v>7.2572319445</v>
+        <v>7.233380740800001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09310883158861834</v>
+        <v>0.09358851995406281</v>
       </c>
       <c r="T17">
-        <v>1.092582715672479</v>
+        <v>1.103660968916</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>19.71947995787455</v>
+        <v>18.4870124605074</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2837,22 +2837,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08529419676141275</v>
+        <v>0.08518353667249992</v>
       </c>
       <c r="C18">
-        <v>48.32851926361653</v>
+        <v>47.78132781385116</v>
       </c>
       <c r="D18">
-        <v>36.56931926361653</v>
+        <v>36.59342781385116</v>
       </c>
       <c r="E18">
-        <v>6.810799999999999</v>
+        <v>7.382099999999999</v>
       </c>
       <c r="F18">
-        <v>9.140799999999999</v>
+        <v>9.7121</v>
       </c>
       <c r="G18">
         <v>20.9</v>
@@ -2873,28 +2873,28 @@
         <v>8.5</v>
       </c>
       <c r="M18">
-        <v>0.4597822399999999</v>
+        <v>0.48851863</v>
       </c>
       <c r="N18">
-        <v>8.040217760000001</v>
+        <v>8.01148137</v>
       </c>
       <c r="O18">
-        <v>1.3668370192</v>
+        <v>1.3619518329</v>
       </c>
       <c r="P18">
-        <v>6.673380740800001</v>
+        <v>6.6495295371</v>
       </c>
       <c r="Q18">
-        <v>7.233380740800001</v>
+        <v>7.209529537100001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09358851995406281</v>
+        <v>0.09407976707530111</v>
       </c>
       <c r="T18">
-        <v>1.103660968916</v>
+        <v>1.115006168020811</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>18.4870124605074</v>
+        <v>17.39954113930107</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2919,22 +2919,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08518353667249992</v>
+        <v>0.0850728765835871</v>
       </c>
       <c r="C19">
-        <v>47.78132781385116</v>
+        <v>47.2341681724778</v>
       </c>
       <c r="D19">
-        <v>36.59342781385116</v>
+        <v>36.6175681724778</v>
       </c>
       <c r="E19">
-        <v>7.382099999999999</v>
+        <v>7.9534</v>
       </c>
       <c r="F19">
-        <v>9.7121</v>
+        <v>10.2834</v>
       </c>
       <c r="G19">
         <v>20.9</v>
@@ -2955,28 +2955,28 @@
         <v>8.5</v>
       </c>
       <c r="M19">
-        <v>0.48851863</v>
+        <v>0.51725502</v>
       </c>
       <c r="N19">
-        <v>8.01148137</v>
+        <v>7.98274498</v>
       </c>
       <c r="O19">
-        <v>1.3619518329</v>
+        <v>1.3570666466</v>
       </c>
       <c r="P19">
-        <v>6.6495295371</v>
+        <v>6.6256783334</v>
       </c>
       <c r="Q19">
-        <v>7.209529537100001</v>
+        <v>7.1856783334</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09407976707530111</v>
+        <v>0.0945829958336428</v>
       </c>
       <c r="T19">
-        <v>1.115006168020811</v>
+        <v>1.12662807929891</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>17.39954113930107</v>
+        <v>16.43289996489546</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3001,22 +3001,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08507287658358709</v>
+        <v>0.08496221649467427</v>
       </c>
       <c r="C20">
-        <v>47.2341681724778</v>
+        <v>46.68704040248916</v>
       </c>
       <c r="D20">
-        <v>36.6175681724778</v>
+        <v>36.64174040248916</v>
       </c>
       <c r="E20">
-        <v>7.953399999999998</v>
+        <v>8.524699999999999</v>
       </c>
       <c r="F20">
-        <v>10.2834</v>
+        <v>10.8547</v>
       </c>
       <c r="G20">
         <v>20.9</v>
@@ -3037,28 +3037,28 @@
         <v>8.5</v>
       </c>
       <c r="M20">
-        <v>0.5172550199999999</v>
+        <v>0.54599141</v>
       </c>
       <c r="N20">
-        <v>7.98274498</v>
+        <v>7.95400859</v>
       </c>
       <c r="O20">
-        <v>1.3570666466</v>
+        <v>1.3521814603</v>
       </c>
       <c r="P20">
-        <v>6.6256783334</v>
+        <v>6.6018271297</v>
       </c>
       <c r="Q20">
-        <v>7.1856783334</v>
+        <v>7.161827129700001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0945829958336428</v>
+        <v>0.09509864999342502</v>
       </c>
       <c r="T20">
-        <v>1.12662807929891</v>
+        <v>1.138536951349308</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.43289996489546</v>
+        <v>15.56801049305886</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3083,22 +3083,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08496221649467427</v>
+        <v>0.08485155640576146</v>
       </c>
       <c r="C21">
-        <v>46.68704040248916</v>
+        <v>46.13994456704437</v>
       </c>
       <c r="D21">
-        <v>36.64174040248916</v>
+        <v>36.66594456704438</v>
       </c>
       <c r="E21">
-        <v>8.524699999999999</v>
+        <v>9.096</v>
       </c>
       <c r="F21">
-        <v>10.8547</v>
+        <v>11.426</v>
       </c>
       <c r="G21">
         <v>20.9</v>
@@ -3119,28 +3119,28 @@
         <v>8.5</v>
       </c>
       <c r="M21">
-        <v>0.54599141</v>
+        <v>0.5747278</v>
       </c>
       <c r="N21">
-        <v>7.95400859</v>
+        <v>7.9252722</v>
       </c>
       <c r="O21">
-        <v>1.3521814603</v>
+        <v>1.347296274</v>
       </c>
       <c r="P21">
-        <v>6.6018271297</v>
+        <v>6.577975926000001</v>
       </c>
       <c r="Q21">
-        <v>7.161827129700001</v>
+        <v>7.137975926000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09509864999342502</v>
+        <v>0.09562719550720181</v>
       </c>
       <c r="T21">
-        <v>1.138536951349308</v>
+        <v>1.150743545200965</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.56801049305886</v>
+        <v>14.78960996840591</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3165,22 +3165,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08485155640576146</v>
+        <v>0.0847408963168486</v>
       </c>
       <c r="C22">
-        <v>46.13994456704437</v>
+        <v>45.59288072946958</v>
       </c>
       <c r="D22">
-        <v>36.66594456704438</v>
+        <v>36.69018072946958</v>
       </c>
       <c r="E22">
-        <v>9.096</v>
+        <v>9.667300000000001</v>
       </c>
       <c r="F22">
-        <v>11.426</v>
+        <v>11.9973</v>
       </c>
       <c r="G22">
         <v>20.9</v>
@@ -3201,28 +3201,28 @@
         <v>8.5</v>
       </c>
       <c r="M22">
-        <v>0.5747278</v>
+        <v>0.6034641900000001</v>
       </c>
       <c r="N22">
-        <v>7.9252722</v>
+        <v>7.89653581</v>
       </c>
       <c r="O22">
-        <v>1.347296274</v>
+        <v>1.3424110877</v>
       </c>
       <c r="P22">
-        <v>6.577975926000001</v>
+        <v>6.554124722299999</v>
       </c>
       <c r="Q22">
-        <v>7.137975926000001</v>
+        <v>7.1141247223</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09562719550720181</v>
+        <v>0.09616912192006152</v>
       </c>
       <c r="T22">
-        <v>1.150743545200965</v>
+        <v>1.16325916674507</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.78960996840591</v>
+        <v>14.08534282705325</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3247,22 +3247,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0847408963168486</v>
+        <v>0.08463023622793579</v>
       </c>
       <c r="C23">
-        <v>45.59288072946958</v>
+        <v>45.04584895325844</v>
       </c>
       <c r="D23">
-        <v>36.69018072946958</v>
+        <v>36.71444895325843</v>
       </c>
       <c r="E23">
-        <v>9.667299999999999</v>
+        <v>10.2386</v>
       </c>
       <c r="F23">
-        <v>11.9973</v>
+        <v>12.5686</v>
       </c>
       <c r="G23">
         <v>20.9</v>
@@ -3283,28 +3283,28 @@
         <v>8.5</v>
       </c>
       <c r="M23">
-        <v>0.60346419</v>
+        <v>0.6322005799999999</v>
       </c>
       <c r="N23">
-        <v>7.89653581</v>
+        <v>7.86779942</v>
       </c>
       <c r="O23">
-        <v>1.3424110877</v>
+        <v>1.3375259014</v>
       </c>
       <c r="P23">
-        <v>6.554124722299999</v>
+        <v>6.5302735186</v>
       </c>
       <c r="Q23">
-        <v>7.1141247223</v>
+        <v>7.0902735186</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09616912192006152</v>
+        <v>0.09672494388196895</v>
       </c>
       <c r="T23">
-        <v>1.16325916674507</v>
+        <v>1.1760957016621</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.08534282705325</v>
+        <v>13.4450999712781</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08463023622793579</v>
+        <v>0.08480592613902294</v>
       </c>
       <c r="C24">
-        <v>45.04584895325844</v>
+        <v>44.43603437600308</v>
       </c>
       <c r="D24">
-        <v>36.71444895325843</v>
+        <v>36.67593437600308</v>
       </c>
       <c r="E24">
-        <v>10.2386</v>
+        <v>10.8099</v>
       </c>
       <c r="F24">
-        <v>12.5686</v>
+        <v>13.1399</v>
       </c>
       <c r="G24">
         <v>20.9</v>
@@ -3365,45 +3365,45 @@
         <v>8.5</v>
       </c>
       <c r="M24">
-        <v>0.6322005799999999</v>
+        <v>0.68064682</v>
       </c>
       <c r="N24">
-        <v>7.86779942</v>
+        <v>7.81935318</v>
       </c>
       <c r="O24">
-        <v>1.3375259014</v>
+        <v>1.3292900406</v>
       </c>
       <c r="P24">
-        <v>6.5302735186</v>
+        <v>6.4900631394</v>
       </c>
       <c r="Q24">
-        <v>7.0902735186</v>
+        <v>7.050063139400001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09672494388196895</v>
+        <v>0.09729520277795187</v>
       </c>
       <c r="T24">
-        <v>1.1760957016621</v>
+        <v>1.189265653070482</v>
       </c>
       <c r="U24">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V24">
         <v>0.17</v>
       </c>
       <c r="W24">
-        <v>0.04174899999999999</v>
+        <v>0.042994</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y24">
-        <v>13.4450999712781</v>
+        <v>12.48812122563064</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3411,22 +3411,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08480592613902294</v>
+        <v>0.08470771605011011</v>
       </c>
       <c r="C25">
-        <v>44.43603437600308</v>
+        <v>43.88625393347181</v>
       </c>
       <c r="D25">
-        <v>36.67593437600308</v>
+        <v>36.69745393347181</v>
       </c>
       <c r="E25">
-        <v>10.8099</v>
+        <v>11.3812</v>
       </c>
       <c r="F25">
-        <v>13.1399</v>
+        <v>13.7112</v>
       </c>
       <c r="G25">
         <v>20.9</v>
@@ -3447,28 +3447,28 @@
         <v>8.5</v>
       </c>
       <c r="M25">
-        <v>0.68064682</v>
+        <v>0.71024016</v>
       </c>
       <c r="N25">
-        <v>7.81935318</v>
+        <v>7.78975984</v>
       </c>
       <c r="O25">
-        <v>1.3292900406</v>
+        <v>1.3242591728</v>
       </c>
       <c r="P25">
-        <v>6.4900631394</v>
+        <v>6.465500667200001</v>
       </c>
       <c r="Q25">
-        <v>7.050063139400001</v>
+        <v>7.025500667200001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09729520277795187</v>
+        <v>0.09788046848698699</v>
       </c>
       <c r="T25">
-        <v>1.189265653070482</v>
+        <v>1.202782182147506</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>12.48812122563064</v>
+        <v>11.96778284122937</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3493,22 +3493,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08470771605011011</v>
+        <v>0.08460950596119729</v>
       </c>
       <c r="C26">
-        <v>43.88625393347181</v>
+        <v>43.33649875891199</v>
       </c>
       <c r="D26">
-        <v>36.69745393347181</v>
+        <v>36.71899875891199</v>
       </c>
       <c r="E26">
-        <v>11.3812</v>
+        <v>11.9525</v>
       </c>
       <c r="F26">
-        <v>13.7112</v>
+        <v>14.2825</v>
       </c>
       <c r="G26">
         <v>20.9</v>
@@ -3529,28 +3529,28 @@
         <v>8.5</v>
       </c>
       <c r="M26">
-        <v>0.7102401599999999</v>
+        <v>0.7398334999999999</v>
       </c>
       <c r="N26">
-        <v>7.78975984</v>
+        <v>7.7601665</v>
       </c>
       <c r="O26">
-        <v>1.3242591728</v>
+        <v>1.319228305</v>
       </c>
       <c r="P26">
-        <v>6.465500667200001</v>
+        <v>6.440938195</v>
       </c>
       <c r="Q26">
-        <v>7.025500667200001</v>
+        <v>7.000938195000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09788046848698699</v>
+        <v>0.09848134128159639</v>
       </c>
       <c r="T26">
-        <v>1.202782182147506</v>
+        <v>1.216659151999916</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.96778284122937</v>
+        <v>11.48907152758019</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3575,22 +3575,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08460950596119729</v>
+        <v>0.08451129587228445</v>
       </c>
       <c r="C27">
-        <v>43.33649875891199</v>
+        <v>42.78676889685374</v>
       </c>
       <c r="D27">
-        <v>36.71899875891199</v>
+        <v>36.74056889685374</v>
       </c>
       <c r="E27">
-        <v>11.9525</v>
+        <v>12.5238</v>
       </c>
       <c r="F27">
-        <v>14.2825</v>
+        <v>14.8538</v>
       </c>
       <c r="G27">
         <v>20.9</v>
@@ -3611,28 +3611,28 @@
         <v>8.5</v>
       </c>
       <c r="M27">
-        <v>0.7398334999999999</v>
+        <v>0.7694268399999999</v>
       </c>
       <c r="N27">
-        <v>7.7601665</v>
+        <v>7.73057316</v>
       </c>
       <c r="O27">
-        <v>1.319228305</v>
+        <v>1.3141974372</v>
       </c>
       <c r="P27">
-        <v>6.440938195</v>
+        <v>6.4163757228</v>
       </c>
       <c r="Q27">
-        <v>7.000938195000001</v>
+        <v>6.9763757228</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09848134128159639</v>
+        <v>0.09909845388146549</v>
       </c>
       <c r="T27">
-        <v>1.216659151999916</v>
+        <v>1.230911175091582</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3649,7 +3649,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.48907152758019</v>
+        <v>11.0471841611348</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3657,22 +3657,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08451129587228445</v>
+        <v>0.08441308578337162</v>
       </c>
       <c r="C28">
-        <v>42.78676889685374</v>
+        <v>42.23706439193185</v>
       </c>
       <c r="D28">
-        <v>36.74056889685374</v>
+        <v>36.76216439193185</v>
       </c>
       <c r="E28">
-        <v>12.5238</v>
+        <v>13.0951</v>
       </c>
       <c r="F28">
-        <v>14.8538</v>
+        <v>15.4251</v>
       </c>
       <c r="G28">
         <v>20.9</v>
@@ -3693,28 +3693,28 @@
         <v>8.5</v>
       </c>
       <c r="M28">
-        <v>0.7694268399999999</v>
+        <v>0.79902018</v>
       </c>
       <c r="N28">
-        <v>7.73057316</v>
+        <v>7.70097982</v>
       </c>
       <c r="O28">
-        <v>1.3141974372</v>
+        <v>1.3091665694</v>
       </c>
       <c r="P28">
-        <v>6.4163757228</v>
+        <v>6.391813250599999</v>
       </c>
       <c r="Q28">
-        <v>6.9763757228</v>
+        <v>6.9518132506</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09909845388146549</v>
+        <v>0.09973247367585153</v>
       </c>
       <c r="T28">
-        <v>1.230911175091582</v>
+        <v>1.245553664569319</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.0471841611348</v>
+        <v>10.63802919220388</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3739,22 +3739,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08441308578337162</v>
+        <v>0.08431487569445879</v>
       </c>
       <c r="C29">
-        <v>42.23706439193185</v>
+        <v>41.68738528888611</v>
       </c>
       <c r="D29">
-        <v>36.76216439193185</v>
+        <v>36.78378528888611</v>
       </c>
       <c r="E29">
-        <v>13.0951</v>
+        <v>13.6664</v>
       </c>
       <c r="F29">
-        <v>15.4251</v>
+        <v>15.9964</v>
       </c>
       <c r="G29">
         <v>20.9</v>
@@ -3775,28 +3775,28 @@
         <v>8.5</v>
       </c>
       <c r="M29">
-        <v>0.79902018</v>
+        <v>0.82861352</v>
       </c>
       <c r="N29">
-        <v>7.70097982</v>
+        <v>7.67138648</v>
       </c>
       <c r="O29">
-        <v>1.3091665694</v>
+        <v>1.3041357016</v>
       </c>
       <c r="P29">
-        <v>6.391813250599999</v>
+        <v>6.3672507784</v>
       </c>
       <c r="Q29">
-        <v>6.9518132506</v>
+        <v>6.9272507784</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09973247367585153</v>
+        <v>0.1003841051311928</v>
       </c>
       <c r="T29">
-        <v>1.245553664569319</v>
+        <v>1.260602889865884</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.63802919220388</v>
+        <v>10.2580995781966</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3821,22 +3821,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08431487569445879</v>
+        <v>0.08421666560554596</v>
       </c>
       <c r="C30">
-        <v>41.68738528888611</v>
+        <v>41.13773163256167</v>
       </c>
       <c r="D30">
-        <v>36.78378528888611</v>
+        <v>36.80543163256168</v>
       </c>
       <c r="E30">
-        <v>13.6664</v>
+        <v>14.2377</v>
       </c>
       <c r="F30">
-        <v>15.9964</v>
+        <v>16.5677</v>
       </c>
       <c r="G30">
         <v>20.9</v>
@@ -3857,28 +3857,28 @@
         <v>8.5</v>
       </c>
       <c r="M30">
-        <v>0.82861352</v>
+        <v>0.8582068600000001</v>
       </c>
       <c r="N30">
-        <v>7.67138648</v>
+        <v>7.64179314</v>
       </c>
       <c r="O30">
-        <v>1.3041357016</v>
+        <v>1.2991048338</v>
       </c>
       <c r="P30">
-        <v>6.3672507784</v>
+        <v>6.342688306199999</v>
       </c>
       <c r="Q30">
-        <v>6.9272507784</v>
+        <v>6.9026883062</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1003841051311928</v>
+        <v>0.1010540924021774</v>
       </c>
       <c r="T30">
-        <v>1.260602889865884</v>
+        <v>1.276076037001788</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.2580995781966</v>
+        <v>9.904372006534647</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3903,22 +3903,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08421666560554594</v>
+        <v>0.08454175551663311</v>
       </c>
       <c r="C31">
-        <v>41.1377316325617</v>
+        <v>40.49487625516205</v>
       </c>
       <c r="D31">
-        <v>36.80543163256169</v>
+        <v>36.73387625516206</v>
       </c>
       <c r="E31">
-        <v>14.2377</v>
+        <v>14.809</v>
       </c>
       <c r="F31">
-        <v>16.5677</v>
+        <v>17.139</v>
       </c>
       <c r="G31">
         <v>20.9</v>
@@ -3939,45 +3939,45 @@
         <v>8.5</v>
       </c>
       <c r="M31">
-        <v>0.8582068599999999</v>
+        <v>0.9169364999999999</v>
       </c>
       <c r="N31">
-        <v>7.64179314</v>
+        <v>7.5830635</v>
       </c>
       <c r="O31">
-        <v>1.2991048338</v>
+        <v>1.289120795</v>
       </c>
       <c r="P31">
-        <v>6.342688306199999</v>
+        <v>6.293942704999999</v>
       </c>
       <c r="Q31">
-        <v>6.9026883062</v>
+        <v>6.853942705</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1010540924021774</v>
+        <v>0.1017432221666187</v>
       </c>
       <c r="T31">
-        <v>1.276076037001788</v>
+        <v>1.29199127405586</v>
       </c>
       <c r="U31">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V31">
         <v>0.17</v>
       </c>
       <c r="W31">
-        <v>0.042994</v>
+        <v>0.044405</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>9.904372006534649</v>
+        <v>9.269998522253177</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3985,22 +3985,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08454175551663311</v>
+        <v>0.0844576554277203</v>
       </c>
       <c r="C32">
-        <v>40.49487625516205</v>
+        <v>39.9420607916951</v>
       </c>
       <c r="D32">
-        <v>36.73387625516206</v>
+        <v>36.7523607916951</v>
       </c>
       <c r="E32">
-        <v>14.809</v>
+        <v>15.3803</v>
       </c>
       <c r="F32">
-        <v>17.139</v>
+        <v>17.7103</v>
       </c>
       <c r="G32">
         <v>20.9</v>
@@ -4021,28 +4021,28 @@
         <v>8.5</v>
       </c>
       <c r="M32">
-        <v>0.9169364999999999</v>
+        <v>0.94750105</v>
       </c>
       <c r="N32">
-        <v>7.5830635</v>
+        <v>7.55249895</v>
       </c>
       <c r="O32">
-        <v>1.289120795</v>
+        <v>1.2839248215</v>
       </c>
       <c r="P32">
-        <v>6.293942704999999</v>
+        <v>6.2685741285</v>
       </c>
       <c r="Q32">
-        <v>6.853942705</v>
+        <v>6.828574128500001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1017432221666187</v>
+        <v>0.102452326706841</v>
       </c>
       <c r="T32">
-        <v>1.29199127405586</v>
+        <v>1.308367822328892</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>9.269998522253177</v>
+        <v>8.970966311857914</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4067,22 +4067,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0844576554277203</v>
+        <v>0.08437355533880747</v>
       </c>
       <c r="C33">
-        <v>39.9420607916951</v>
+        <v>39.38926394048173</v>
       </c>
       <c r="D33">
-        <v>36.7523607916951</v>
+        <v>36.77086394048173</v>
       </c>
       <c r="E33">
-        <v>15.3803</v>
+        <v>15.9516</v>
       </c>
       <c r="F33">
-        <v>17.7103</v>
+        <v>18.2816</v>
       </c>
       <c r="G33">
         <v>20.9</v>
@@ -4103,28 +4103,28 @@
         <v>8.5</v>
       </c>
       <c r="M33">
-        <v>0.94750105</v>
+        <v>0.9780655999999999</v>
       </c>
       <c r="N33">
-        <v>7.55249895</v>
+        <v>7.5219344</v>
       </c>
       <c r="O33">
-        <v>1.2839248215</v>
+        <v>1.278728848</v>
       </c>
       <c r="P33">
-        <v>6.2685741285</v>
+        <v>6.243205552</v>
       </c>
       <c r="Q33">
-        <v>6.828574128500001</v>
+        <v>6.803205552000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.102452326706841</v>
+        <v>0.1031822872629522</v>
       </c>
       <c r="T33">
-        <v>1.308367822328892</v>
+        <v>1.325226033786424</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.970966311857914</v>
+        <v>8.690623614612354</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4149,22 +4149,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08437355533880747</v>
+        <v>0.08428945524989463</v>
       </c>
       <c r="C34">
-        <v>39.38926394048173</v>
+        <v>38.83648572964741</v>
       </c>
       <c r="D34">
-        <v>36.77086394048173</v>
+        <v>36.78938572964741</v>
       </c>
       <c r="E34">
-        <v>15.9516</v>
+        <v>16.5229</v>
       </c>
       <c r="F34">
-        <v>18.2816</v>
+        <v>18.8529</v>
       </c>
       <c r="G34">
         <v>20.9</v>
@@ -4185,28 +4185,28 @@
         <v>8.5</v>
       </c>
       <c r="M34">
-        <v>0.9780655999999999</v>
+        <v>1.00863015</v>
       </c>
       <c r="N34">
-        <v>7.5219344</v>
+        <v>7.49136985</v>
       </c>
       <c r="O34">
-        <v>1.278728848</v>
+        <v>1.2735328745</v>
       </c>
       <c r="P34">
-        <v>6.243205552</v>
+        <v>6.2178369755</v>
       </c>
       <c r="Q34">
-        <v>6.803205552000001</v>
+        <v>6.777836975500001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1031822872629522</v>
+        <v>0.1039340376864099</v>
       </c>
       <c r="T34">
-        <v>1.325226033786424</v>
+        <v>1.342587475436719</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.690623614612354</v>
+        <v>8.427271383866525</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4231,22 +4231,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08428945524989463</v>
+        <v>0.08420535516098181</v>
       </c>
       <c r="C35">
-        <v>38.83648572964741</v>
+        <v>38.28372618737426</v>
       </c>
       <c r="D35">
-        <v>36.78938572964741</v>
+        <v>36.80792618737426</v>
       </c>
       <c r="E35">
-        <v>16.5229</v>
+        <v>17.0942</v>
       </c>
       <c r="F35">
-        <v>18.8529</v>
+        <v>19.4242</v>
       </c>
       <c r="G35">
         <v>20.9</v>
@@ -4267,28 +4267,28 @@
         <v>8.5</v>
       </c>
       <c r="M35">
-        <v>1.00863015</v>
+        <v>1.0391947</v>
       </c>
       <c r="N35">
-        <v>7.49136985</v>
+        <v>7.460805300000001</v>
       </c>
       <c r="O35">
-        <v>1.2735328745</v>
+        <v>1.268336901</v>
       </c>
       <c r="P35">
-        <v>6.2178369755</v>
+        <v>6.192468399000001</v>
       </c>
       <c r="Q35">
-        <v>6.777836975500001</v>
+        <v>6.752468399000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1039340376864099</v>
+        <v>0.10470856842573</v>
       </c>
       <c r="T35">
-        <v>1.342587475436719</v>
+        <v>1.360475021379446</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.427271383866525</v>
+        <v>8.179410460811628</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4313,22 +4313,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08420535516098181</v>
+        <v>0.08412125507206898</v>
       </c>
       <c r="C36">
-        <v>38.28372618737426</v>
+        <v>37.73098534190127</v>
       </c>
       <c r="D36">
-        <v>36.80792618737426</v>
+        <v>36.82648534190127</v>
       </c>
       <c r="E36">
-        <v>17.0942</v>
+        <v>17.6655</v>
       </c>
       <c r="F36">
-        <v>19.4242</v>
+        <v>19.9955</v>
       </c>
       <c r="G36">
         <v>20.9</v>
@@ -4349,28 +4349,28 @@
         <v>8.5</v>
       </c>
       <c r="M36">
-        <v>1.0391947</v>
+        <v>1.06975925</v>
       </c>
       <c r="N36">
-        <v>7.460805300000001</v>
+        <v>7.43024075</v>
       </c>
       <c r="O36">
-        <v>1.268336901</v>
+        <v>1.2631409275</v>
       </c>
       <c r="P36">
-        <v>6.192468399000001</v>
+        <v>6.1670998225</v>
       </c>
       <c r="Q36">
-        <v>6.752468399000001</v>
+        <v>6.7270998225</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.10470856842573</v>
+        <v>0.1055069308801061</v>
       </c>
       <c r="T36">
-        <v>1.360475021379446</v>
+        <v>1.378912953351181</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.179410460811628</v>
+        <v>7.945713019074153</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08412125507206898</v>
+        <v>0.08403715498315614</v>
       </c>
       <c r="C37">
-        <v>37.73098534190127</v>
+        <v>37.17826322152439</v>
       </c>
       <c r="D37">
-        <v>36.82648534190127</v>
+        <v>36.84506322152439</v>
       </c>
       <c r="E37">
-        <v>17.6655</v>
+        <v>18.2368</v>
       </c>
       <c r="F37">
-        <v>19.9955</v>
+        <v>20.5668</v>
       </c>
       <c r="G37">
         <v>20.9</v>
@@ -4431,28 +4431,28 @@
         <v>8.5</v>
       </c>
       <c r="M37">
-        <v>1.06975925</v>
+        <v>1.1003238</v>
       </c>
       <c r="N37">
-        <v>7.43024075</v>
+        <v>7.3996762</v>
       </c>
       <c r="O37">
-        <v>1.2631409275</v>
+        <v>1.257944954</v>
       </c>
       <c r="P37">
-        <v>6.1670998225</v>
+        <v>6.141731246</v>
       </c>
       <c r="Q37">
-        <v>6.7270998225</v>
+        <v>6.701731246</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1055069308801061</v>
+        <v>0.1063302421611815</v>
       </c>
       <c r="T37">
-        <v>1.378912953351181</v>
+        <v>1.397927070697032</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.945713019074153</v>
+        <v>7.724998768544314</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4477,22 +4477,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08403715498315614</v>
+        <v>0.08419873489424332</v>
       </c>
       <c r="C38">
-        <v>37.17826322152439</v>
+        <v>36.57128646532313</v>
       </c>
       <c r="D38">
-        <v>36.84506322152439</v>
+        <v>36.80938646532312</v>
       </c>
       <c r="E38">
-        <v>18.2368</v>
+        <v>18.8081</v>
       </c>
       <c r="F38">
-        <v>20.5668</v>
+        <v>21.1381</v>
       </c>
       <c r="G38">
         <v>20.9</v>
@@ -4513,45 +4513,45 @@
         <v>8.5</v>
       </c>
       <c r="M38">
-        <v>1.1003238</v>
+        <v>1.14779883</v>
       </c>
       <c r="N38">
-        <v>7.3996762</v>
+        <v>7.35220117</v>
       </c>
       <c r="O38">
-        <v>1.257944954</v>
+        <v>1.2498741989</v>
       </c>
       <c r="P38">
-        <v>6.141731246</v>
+        <v>6.1023269711</v>
       </c>
       <c r="Q38">
-        <v>6.701731246</v>
+        <v>6.662326971100001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1063302421611815</v>
+        <v>0.1071796903083227</v>
       </c>
       <c r="T38">
-        <v>1.397927070697032</v>
+        <v>1.417544810815767</v>
       </c>
       <c r="U38">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V38">
         <v>0.17</v>
       </c>
       <c r="W38">
-        <v>0.044405</v>
+        <v>0.045069</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y38">
-        <v>7.724998768544316</v>
+        <v>7.405478885180603</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4559,22 +4559,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08419873489424332</v>
+        <v>0.08412127480533048</v>
       </c>
       <c r="C39">
-        <v>36.57128646532313</v>
+        <v>36.01708098498237</v>
       </c>
       <c r="D39">
-        <v>36.80938646532312</v>
+        <v>36.82648098498237</v>
       </c>
       <c r="E39">
-        <v>18.8081</v>
+        <v>19.3794</v>
       </c>
       <c r="F39">
-        <v>21.1381</v>
+        <v>21.7094</v>
       </c>
       <c r="G39">
         <v>20.9</v>
@@ -4595,28 +4595,28 @@
         <v>8.5</v>
       </c>
       <c r="M39">
-        <v>1.14779883</v>
+        <v>1.17882042</v>
       </c>
       <c r="N39">
-        <v>7.35220117</v>
+        <v>7.32117958</v>
       </c>
       <c r="O39">
-        <v>1.2498741989</v>
+        <v>1.2446005286</v>
       </c>
       <c r="P39">
-        <v>6.1023269711</v>
+        <v>6.0765790514</v>
       </c>
       <c r="Q39">
-        <v>6.662326971100001</v>
+        <v>6.6365790514</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1071796903083227</v>
+        <v>0.1080565400085976</v>
       </c>
       <c r="T39">
-        <v>1.417544810815767</v>
+        <v>1.437795381260914</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4633,7 +4633,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.405478885180603</v>
+        <v>7.210597861886376</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4641,22 +4641,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08412127480533048</v>
+        <v>0.08404381471641766</v>
       </c>
       <c r="C40">
-        <v>36.01708098498237</v>
+        <v>35.46289138963203</v>
       </c>
       <c r="D40">
-        <v>36.82648098498237</v>
+        <v>36.84359138963203</v>
       </c>
       <c r="E40">
-        <v>19.3794</v>
+        <v>19.9507</v>
       </c>
       <c r="F40">
-        <v>21.7094</v>
+        <v>22.2807</v>
       </c>
       <c r="G40">
         <v>20.9</v>
@@ -4677,28 +4677,28 @@
         <v>8.5</v>
       </c>
       <c r="M40">
-        <v>1.17882042</v>
+        <v>1.20984201</v>
       </c>
       <c r="N40">
-        <v>7.32117958</v>
+        <v>7.29015799</v>
       </c>
       <c r="O40">
-        <v>1.2446005286</v>
+        <v>1.2393268583</v>
       </c>
       <c r="P40">
-        <v>6.0765790514</v>
+        <v>6.0508311317</v>
       </c>
       <c r="Q40">
-        <v>6.6365790514</v>
+        <v>6.6108311317</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1080565400085976</v>
+        <v>0.1089621388793732</v>
       </c>
       <c r="T40">
-        <v>1.437795381260914</v>
+        <v>1.458709904835409</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4715,7 +4715,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.210597861886376</v>
+        <v>7.025710737222623</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4723,22 +4723,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08404381471641766</v>
+        <v>0.08396635462750482</v>
       </c>
       <c r="C41">
-        <v>35.46289138963203</v>
+        <v>34.90871770142395</v>
       </c>
       <c r="D41">
-        <v>36.84359138963203</v>
+        <v>36.86071770142396</v>
       </c>
       <c r="E41">
-        <v>19.9507</v>
+        <v>20.522</v>
       </c>
       <c r="F41">
-        <v>22.2807</v>
+        <v>22.852</v>
       </c>
       <c r="G41">
         <v>20.9</v>
@@ -4759,28 +4759,28 @@
         <v>8.5</v>
       </c>
       <c r="M41">
-        <v>1.20984201</v>
+        <v>1.2408636</v>
       </c>
       <c r="N41">
-        <v>7.29015799</v>
+        <v>7.2591364</v>
       </c>
       <c r="O41">
-        <v>1.2393268583</v>
+        <v>1.234053188</v>
       </c>
       <c r="P41">
-        <v>6.0508311317</v>
+        <v>6.025083212</v>
       </c>
       <c r="Q41">
-        <v>6.6108311317</v>
+        <v>6.585083212000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1089621388793732</v>
+        <v>0.1098979243791747</v>
       </c>
       <c r="T41">
-        <v>1.458709904835409</v>
+        <v>1.48032157919572</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4797,7 +4797,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.025710737222623</v>
+        <v>6.850067968792057</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4805,22 +4805,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08396635462750482</v>
+        <v>0.083888894538592</v>
       </c>
       <c r="C42">
-        <v>34.90871770142395</v>
+        <v>34.35455994255121</v>
       </c>
       <c r="D42">
-        <v>36.86071770142396</v>
+        <v>36.87785994255121</v>
       </c>
       <c r="E42">
-        <v>20.522</v>
+        <v>21.0933</v>
       </c>
       <c r="F42">
-        <v>22.852</v>
+        <v>23.4233</v>
       </c>
       <c r="G42">
         <v>20.9</v>
@@ -4841,28 +4841,28 @@
         <v>8.5</v>
       </c>
       <c r="M42">
-        <v>1.2408636</v>
+        <v>1.27188519</v>
       </c>
       <c r="N42">
-        <v>7.2591364</v>
+        <v>7.22811481</v>
       </c>
       <c r="O42">
-        <v>1.234053188</v>
+        <v>1.2287795177</v>
       </c>
       <c r="P42">
-        <v>6.025083212</v>
+        <v>5.9993352923</v>
       </c>
       <c r="Q42">
-        <v>6.585083212000001</v>
+        <v>6.5593352923</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1098979243791747</v>
+        <v>0.1108654314213424</v>
       </c>
       <c r="T42">
-        <v>1.48032157919572</v>
+        <v>1.502665852686891</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.850067968792057</v>
+        <v>6.682993140284934</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4887,22 +4887,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.083888894538592</v>
+        <v>0.08381143444967916</v>
       </c>
       <c r="C43">
-        <v>34.35455994255121</v>
+        <v>33.80041813524815</v>
       </c>
       <c r="D43">
-        <v>36.87785994255121</v>
+        <v>36.89501813524816</v>
       </c>
       <c r="E43">
-        <v>21.0933</v>
+        <v>21.6646</v>
       </c>
       <c r="F43">
-        <v>23.4233</v>
+        <v>23.9946</v>
       </c>
       <c r="G43">
         <v>20.9</v>
@@ -4923,28 +4923,28 @@
         <v>8.5</v>
       </c>
       <c r="M43">
-        <v>1.27188519</v>
+        <v>1.30290678</v>
       </c>
       <c r="N43">
-        <v>7.22811481</v>
+        <v>7.19709322</v>
       </c>
       <c r="O43">
-        <v>1.2287795177</v>
+        <v>1.2235058474</v>
       </c>
       <c r="P43">
-        <v>5.9993352923</v>
+        <v>5.9735873726</v>
       </c>
       <c r="Q43">
-        <v>6.5593352923</v>
+        <v>6.5335873726</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1108654314213424</v>
+        <v>0.1118663007753089</v>
       </c>
       <c r="T43">
-        <v>1.502665852686891</v>
+        <v>1.525780618367411</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.682993140284934</v>
+        <v>6.523874255992435</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08381143444967917</v>
+        <v>0.08373397436076634</v>
       </c>
       <c r="C44">
-        <v>33.80041813524815</v>
+        <v>33.24629230179056</v>
       </c>
       <c r="D44">
-        <v>36.89501813524815</v>
+        <v>36.91219230179056</v>
       </c>
       <c r="E44">
-        <v>21.6646</v>
+        <v>22.2359</v>
       </c>
       <c r="F44">
-        <v>23.9946</v>
+        <v>24.5659</v>
       </c>
       <c r="G44">
         <v>20.9</v>
@@ -5005,28 +5005,28 @@
         <v>8.5</v>
       </c>
       <c r="M44">
-        <v>1.30290678</v>
+        <v>1.33392837</v>
       </c>
       <c r="N44">
-        <v>7.19709322</v>
+        <v>7.16607163</v>
       </c>
       <c r="O44">
-        <v>1.2235058474</v>
+        <v>1.2182321771</v>
       </c>
       <c r="P44">
-        <v>5.9735873726</v>
+        <v>5.9478394529</v>
       </c>
       <c r="Q44">
-        <v>6.5335873726</v>
+        <v>6.507839452900001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1118663007753089</v>
+        <v>0.1129022883522216</v>
       </c>
       <c r="T44">
-        <v>1.525780618367411</v>
+        <v>1.549706428457774</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.523874255992435</v>
+        <v>6.372156250039123</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5051,22 +5051,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08373397436076634</v>
+        <v>0.0836565142718535</v>
       </c>
       <c r="C45">
-        <v>33.24629230179056</v>
+        <v>32.69218246449569</v>
       </c>
       <c r="D45">
-        <v>36.91219230179056</v>
+        <v>36.92938246449569</v>
       </c>
       <c r="E45">
-        <v>22.2359</v>
+        <v>22.80719999999999</v>
       </c>
       <c r="F45">
-        <v>24.5659</v>
+        <v>25.1372</v>
       </c>
       <c r="G45">
         <v>20.9</v>
@@ -5087,28 +5087,28 @@
         <v>8.5</v>
       </c>
       <c r="M45">
-        <v>1.33392837</v>
+        <v>1.36494996</v>
       </c>
       <c r="N45">
-        <v>7.16607163</v>
+        <v>7.13505004</v>
       </c>
       <c r="O45">
-        <v>1.2182321771</v>
+        <v>1.2129585068</v>
       </c>
       <c r="P45">
-        <v>5.9478394529</v>
+        <v>5.9220915332</v>
       </c>
       <c r="Q45">
-        <v>6.507839452900001</v>
+        <v>6.4820915332</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1129022883522216</v>
+        <v>0.1139752754854527</v>
       </c>
       <c r="T45">
-        <v>1.549706428457774</v>
+        <v>1.574486731765651</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.372156250039123</v>
+        <v>6.22733451708369</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5133,22 +5133,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0836565142718535</v>
+        <v>0.08395255418294068</v>
       </c>
       <c r="C46">
-        <v>32.69218246449569</v>
+        <v>32.05527063060487</v>
       </c>
       <c r="D46">
-        <v>36.92938246449569</v>
+        <v>36.86377063060487</v>
       </c>
       <c r="E46">
-        <v>22.80719999999999</v>
+        <v>23.3785</v>
       </c>
       <c r="F46">
-        <v>25.1372</v>
+        <v>25.7085</v>
       </c>
       <c r="G46">
         <v>20.9</v>
@@ -5169,45 +5169,45 @@
         <v>8.5</v>
       </c>
       <c r="M46">
-        <v>1.36494996</v>
+        <v>1.42168005</v>
       </c>
       <c r="N46">
-        <v>7.13505004</v>
+        <v>7.07831995</v>
       </c>
       <c r="O46">
-        <v>1.2129585068</v>
+        <v>1.2033143915</v>
       </c>
       <c r="P46">
-        <v>5.9220915332</v>
+        <v>5.8750055585</v>
       </c>
       <c r="Q46">
-        <v>6.4820915332</v>
+        <v>6.4350055585</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1139752754854527</v>
+        <v>0.1150872803326194</v>
       </c>
       <c r="T46">
-        <v>1.574486731765651</v>
+        <v>1.600168137011995</v>
       </c>
       <c r="U46">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V46">
         <v>0.17</v>
       </c>
       <c r="W46">
-        <v>0.045069</v>
+        <v>0.045899</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>6.22733451708369</v>
+        <v>5.978841723213321</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5215,22 +5215,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08395255418294068</v>
+        <v>0.08388339409402784</v>
       </c>
       <c r="C47">
-        <v>32.05527063060487</v>
+        <v>31.49927782021762</v>
       </c>
       <c r="D47">
-        <v>36.86377063060487</v>
+        <v>36.87907782021762</v>
       </c>
       <c r="E47">
-        <v>23.3785</v>
+        <v>23.9498</v>
       </c>
       <c r="F47">
-        <v>25.7085</v>
+        <v>26.2798</v>
       </c>
       <c r="G47">
         <v>20.9</v>
@@ -5251,28 +5251,28 @@
         <v>8.5</v>
       </c>
       <c r="M47">
-        <v>1.42168005</v>
+        <v>1.45327294</v>
       </c>
       <c r="N47">
-        <v>7.07831995</v>
+        <v>7.04672706</v>
       </c>
       <c r="O47">
-        <v>1.2033143915</v>
+        <v>1.1979436002</v>
       </c>
       <c r="P47">
-        <v>5.8750055585</v>
+        <v>5.8487834598</v>
       </c>
       <c r="Q47">
-        <v>6.4350055585</v>
+        <v>6.4087834598</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1150872803326194</v>
+        <v>0.116240470544496</v>
       </c>
       <c r="T47">
-        <v>1.600168137011995</v>
+        <v>1.626800705415612</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.978841723213321</v>
+        <v>5.848866903143466</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5297,22 +5297,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08388339409402784</v>
+        <v>0.08381423400511501</v>
       </c>
       <c r="C48">
-        <v>31.49927782021762</v>
+        <v>30.94329772732422</v>
       </c>
       <c r="D48">
-        <v>36.87907782021762</v>
+        <v>36.89439772732422</v>
       </c>
       <c r="E48">
-        <v>23.9498</v>
+        <v>24.5211</v>
       </c>
       <c r="F48">
-        <v>26.2798</v>
+        <v>26.8511</v>
       </c>
       <c r="G48">
         <v>20.9</v>
@@ -5333,28 +5333,28 @@
         <v>8.5</v>
       </c>
       <c r="M48">
-        <v>1.45327294</v>
+        <v>1.48486583</v>
       </c>
       <c r="N48">
-        <v>7.04672706</v>
+        <v>7.01513417</v>
       </c>
       <c r="O48">
-        <v>1.1979436002</v>
+        <v>1.1925728089</v>
       </c>
       <c r="P48">
-        <v>5.8487834598</v>
+        <v>5.8225613611</v>
       </c>
       <c r="Q48">
-        <v>6.4087834598</v>
+        <v>6.3825613611</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.116240470544496</v>
+        <v>0.1174371773681415</v>
       </c>
       <c r="T48">
-        <v>1.626800705415612</v>
+        <v>1.654438276400497</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.848866903143466</v>
+        <v>5.724422926480839</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5379,22 +5379,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08381423400511501</v>
+        <v>0.08374507391620217</v>
       </c>
       <c r="C49">
-        <v>30.94329772732422</v>
+        <v>30.38733036778016</v>
       </c>
       <c r="D49">
-        <v>36.89439772732422</v>
+        <v>36.90973036778016</v>
       </c>
       <c r="E49">
-        <v>24.5211</v>
+        <v>25.0924</v>
       </c>
       <c r="F49">
-        <v>26.8511</v>
+        <v>27.4224</v>
       </c>
       <c r="G49">
         <v>20.9</v>
@@ -5415,28 +5415,28 @@
         <v>8.5</v>
       </c>
       <c r="M49">
-        <v>1.48486583</v>
+        <v>1.51645872</v>
       </c>
       <c r="N49">
-        <v>7.01513417</v>
+        <v>6.98354128</v>
       </c>
       <c r="O49">
-        <v>1.1925728089</v>
+        <v>1.1872020176</v>
       </c>
       <c r="P49">
-        <v>5.8225613611</v>
+        <v>5.7963392624</v>
       </c>
       <c r="Q49">
-        <v>6.3825613611</v>
+        <v>6.356339262400001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1174371773681415</v>
+        <v>0.1186799113773119</v>
       </c>
       <c r="T49">
-        <v>1.654438276400497</v>
+        <v>1.683138830884801</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.724422926480839</v>
+        <v>5.605164115512489</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08374507391620217</v>
+        <v>0.08367591382728935</v>
       </c>
       <c r="C50">
-        <v>30.38733036778017</v>
+        <v>29.8313757574673</v>
       </c>
       <c r="D50">
-        <v>36.90973036778016</v>
+        <v>36.9250757574673</v>
       </c>
       <c r="E50">
-        <v>25.0924</v>
+        <v>25.6637</v>
       </c>
       <c r="F50">
-        <v>27.4224</v>
+        <v>27.9937</v>
       </c>
       <c r="G50">
         <v>20.9</v>
@@ -5497,28 +5497,28 @@
         <v>8.5</v>
       </c>
       <c r="M50">
-        <v>1.51645872</v>
+        <v>1.54805161</v>
       </c>
       <c r="N50">
-        <v>6.98354128</v>
+        <v>6.95194839</v>
       </c>
       <c r="O50">
-        <v>1.1872020176</v>
+        <v>1.1818312263</v>
       </c>
       <c r="P50">
-        <v>5.7963392624</v>
+        <v>5.7701171637</v>
       </c>
       <c r="Q50">
-        <v>6.356339262400001</v>
+        <v>6.330117163700001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1186799113773119</v>
+        <v>0.1199713800535085</v>
       </c>
       <c r="T50">
-        <v>1.683138830884801</v>
+        <v>1.712964897309666</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.605164115512489</v>
+        <v>5.490773011114275</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5543,22 +5543,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08367591382728935</v>
+        <v>0.08360675373837652</v>
       </c>
       <c r="C51">
-        <v>29.8313757574673</v>
+        <v>29.27543391229388</v>
       </c>
       <c r="D51">
-        <v>36.9250757574673</v>
+        <v>36.94043391229388</v>
       </c>
       <c r="E51">
-        <v>25.6637</v>
+        <v>26.235</v>
       </c>
       <c r="F51">
-        <v>27.9937</v>
+        <v>28.565</v>
       </c>
       <c r="G51">
         <v>20.9</v>
@@ -5579,28 +5579,28 @@
         <v>8.5</v>
       </c>
       <c r="M51">
-        <v>1.54805161</v>
+        <v>1.5796445</v>
       </c>
       <c r="N51">
-        <v>6.95194839</v>
+        <v>6.9203555</v>
       </c>
       <c r="O51">
-        <v>1.1818312263</v>
+        <v>1.176460435</v>
       </c>
       <c r="P51">
-        <v>5.7701171637</v>
+        <v>5.743895065</v>
       </c>
       <c r="Q51">
-        <v>6.330117163700001</v>
+        <v>6.303895065000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1199713800535085</v>
+        <v>0.121314507476753</v>
       </c>
       <c r="T51">
-        <v>1.712964897309666</v>
+        <v>1.743984006391525</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.490773011114275</v>
+        <v>5.380957550891989</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5625,22 +5625,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08360675373837652</v>
+        <v>0.08353759364946368</v>
       </c>
       <c r="C52">
-        <v>29.27543391229388</v>
+        <v>28.71950484819467</v>
       </c>
       <c r="D52">
-        <v>36.94043391229388</v>
+        <v>36.95580484819467</v>
       </c>
       <c r="E52">
-        <v>26.235</v>
+        <v>26.8063</v>
       </c>
       <c r="F52">
-        <v>28.565</v>
+        <v>29.1363</v>
       </c>
       <c r="G52">
         <v>20.9</v>
@@ -5661,28 +5661,28 @@
         <v>8.5</v>
       </c>
       <c r="M52">
-        <v>1.5796445</v>
+        <v>1.61123739</v>
       </c>
       <c r="N52">
-        <v>6.9203555</v>
+        <v>6.888762610000001</v>
       </c>
       <c r="O52">
-        <v>1.176460435</v>
+        <v>1.1710896437</v>
       </c>
       <c r="P52">
-        <v>5.743895065</v>
+        <v>5.7176729663</v>
       </c>
       <c r="Q52">
-        <v>6.303895065000001</v>
+        <v>6.277672966300001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.121314507476753</v>
+        <v>0.1227124564274769</v>
       </c>
       <c r="T52">
-        <v>1.743984006391525</v>
+        <v>1.776269201558358</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5699,7 +5699,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.380957550891989</v>
+        <v>5.275448579305872</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5707,22 +5707,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08353759364946368</v>
+        <v>0.08346843356055086</v>
       </c>
       <c r="C53">
-        <v>28.71950484819467</v>
+        <v>28.16358858113092</v>
       </c>
       <c r="D53">
-        <v>36.95580484819467</v>
+        <v>36.97118858113092</v>
       </c>
       <c r="E53">
-        <v>26.8063</v>
+        <v>27.3776</v>
       </c>
       <c r="F53">
-        <v>29.1363</v>
+        <v>29.7076</v>
       </c>
       <c r="G53">
         <v>20.9</v>
@@ -5743,28 +5743,28 @@
         <v>8.5</v>
       </c>
       <c r="M53">
-        <v>1.61123739</v>
+        <v>1.64283028</v>
       </c>
       <c r="N53">
-        <v>6.888762610000001</v>
+        <v>6.85716972</v>
       </c>
       <c r="O53">
-        <v>1.1710896437</v>
+        <v>1.1657188524</v>
       </c>
       <c r="P53">
-        <v>5.7176729663</v>
+        <v>5.6914508676</v>
       </c>
       <c r="Q53">
-        <v>6.277672966300001</v>
+        <v>6.2514508676</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1227124564274769</v>
+        <v>0.1241686532511476</v>
       </c>
       <c r="T53">
-        <v>1.776269201558358</v>
+        <v>1.809899613190476</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5781,7 +5781,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.275448579305872</v>
+        <v>5.17399764508845</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5789,22 +5789,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08346843356055086</v>
+        <v>0.08339927347163803</v>
       </c>
       <c r="C54">
-        <v>28.16358858113092</v>
+        <v>27.60768512709053</v>
       </c>
       <c r="D54">
-        <v>36.97118858113092</v>
+        <v>36.98658512709053</v>
       </c>
       <c r="E54">
-        <v>27.3776</v>
+        <v>27.9489</v>
       </c>
       <c r="F54">
-        <v>29.7076</v>
+        <v>30.2789</v>
       </c>
       <c r="G54">
         <v>20.9</v>
@@ -5825,28 +5825,28 @@
         <v>8.5</v>
       </c>
       <c r="M54">
-        <v>1.64283028</v>
+        <v>1.67442317</v>
       </c>
       <c r="N54">
-        <v>6.85716972</v>
+        <v>6.82557683</v>
       </c>
       <c r="O54">
-        <v>1.1657188524</v>
+        <v>1.1603480611</v>
       </c>
       <c r="P54">
-        <v>5.6914508676</v>
+        <v>5.6652287689</v>
       </c>
       <c r="Q54">
-        <v>6.2514508676</v>
+        <v>6.225228768900001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1241686532511476</v>
+        <v>0.1256868158971022</v>
       </c>
       <c r="T54">
-        <v>1.809899613190476</v>
+        <v>1.844961106168642</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.17399764508845</v>
+        <v>5.07637504801131</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5871,22 +5871,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08339927347163803</v>
+        <v>0.08333011338272518</v>
       </c>
       <c r="C55">
-        <v>27.60768512709053</v>
+        <v>27.05179450208799</v>
       </c>
       <c r="D55">
-        <v>36.98658512709053</v>
+        <v>37.00199450208799</v>
       </c>
       <c r="E55">
-        <v>27.9489</v>
+        <v>28.5202</v>
       </c>
       <c r="F55">
-        <v>30.2789</v>
+        <v>30.8502</v>
       </c>
       <c r="G55">
         <v>20.9</v>
@@ -5907,28 +5907,28 @@
         <v>8.5</v>
       </c>
       <c r="M55">
-        <v>1.67442317</v>
+        <v>1.70601606</v>
       </c>
       <c r="N55">
-        <v>6.82557683</v>
+        <v>6.79398394</v>
       </c>
       <c r="O55">
-        <v>1.1603480611</v>
+        <v>1.1549772698</v>
       </c>
       <c r="P55">
-        <v>5.6652287689</v>
+        <v>5.639006670200001</v>
       </c>
       <c r="Q55">
-        <v>6.225228768900001</v>
+        <v>6.199006670200001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1256868158971022</v>
+        <v>0.12727098561462</v>
       </c>
       <c r="T55">
-        <v>1.844961106168642</v>
+        <v>1.881547011884988</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5945,7 +5945,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.07637504801131</v>
+        <v>4.982368102677768</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5953,22 +5953,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08333011338272518</v>
+        <v>0.08326095329381236</v>
       </c>
       <c r="C56">
-        <v>27.05179450208799</v>
+        <v>26.49591672216451</v>
       </c>
       <c r="D56">
-        <v>37.00199450208799</v>
+        <v>37.01741672216451</v>
       </c>
       <c r="E56">
-        <v>28.5202</v>
+        <v>29.0915</v>
       </c>
       <c r="F56">
-        <v>30.8502</v>
+        <v>31.4215</v>
       </c>
       <c r="G56">
         <v>20.9</v>
@@ -5989,28 +5989,28 @@
         <v>8.5</v>
       </c>
       <c r="M56">
-        <v>1.70601606</v>
+        <v>1.73760895</v>
       </c>
       <c r="N56">
-        <v>6.79398394</v>
+        <v>6.76239105</v>
       </c>
       <c r="O56">
-        <v>1.1549772698</v>
+        <v>1.1496064785</v>
       </c>
       <c r="P56">
-        <v>5.639006670200001</v>
+        <v>5.6127845715</v>
       </c>
       <c r="Q56">
-        <v>6.199006670200001</v>
+        <v>6.1727845715</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.12727098561462</v>
+        <v>0.1289255628751386</v>
       </c>
       <c r="T56">
-        <v>1.881547011884988</v>
+        <v>1.919758957855395</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.982368102677768</v>
+        <v>4.891779591719989</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6035,22 +6035,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08326095329381236</v>
+        <v>0.08319179320489953</v>
       </c>
       <c r="C57">
-        <v>26.49591672216451</v>
+        <v>25.94005180338807</v>
       </c>
       <c r="D57">
-        <v>37.01741672216451</v>
+        <v>37.03285180338807</v>
       </c>
       <c r="E57">
-        <v>29.0915</v>
+        <v>29.6628</v>
       </c>
       <c r="F57">
-        <v>31.4215</v>
+        <v>31.9928</v>
       </c>
       <c r="G57">
         <v>20.9</v>
@@ -6071,28 +6071,28 @@
         <v>8.5</v>
       </c>
       <c r="M57">
-        <v>1.73760895</v>
+        <v>1.76920184</v>
       </c>
       <c r="N57">
-        <v>6.76239105</v>
+        <v>6.73079816</v>
       </c>
       <c r="O57">
-        <v>1.1496064785</v>
+        <v>1.1442356872</v>
       </c>
       <c r="P57">
-        <v>5.6127845715</v>
+        <v>5.5865624728</v>
       </c>
       <c r="Q57">
-        <v>6.1727845715</v>
+        <v>6.1465624728</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1289255628751386</v>
+        <v>0.1306553481929535</v>
       </c>
       <c r="T57">
-        <v>1.919758957855395</v>
+        <v>1.95970781046082</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6109,7 +6109,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.891779591719989</v>
+        <v>4.80442638472499</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6117,22 +6117,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08319179320489953</v>
+        <v>0.08312263311598669</v>
       </c>
       <c r="C58">
-        <v>25.94005180338807</v>
+        <v>25.38419976185342</v>
       </c>
       <c r="D58">
-        <v>37.03285180338807</v>
+        <v>37.04829976185342</v>
       </c>
       <c r="E58">
-        <v>29.6628</v>
+        <v>30.23410000000001</v>
       </c>
       <c r="F58">
-        <v>31.9928</v>
+        <v>32.5641</v>
       </c>
       <c r="G58">
         <v>20.9</v>
@@ -6153,28 +6153,28 @@
         <v>8.5</v>
       </c>
       <c r="M58">
-        <v>1.76920184</v>
+        <v>1.80079473</v>
       </c>
       <c r="N58">
-        <v>6.73079816</v>
+        <v>6.69920527</v>
       </c>
       <c r="O58">
-        <v>1.1442356872</v>
+        <v>1.1388648959</v>
       </c>
       <c r="P58">
-        <v>5.5865624728</v>
+        <v>5.5603403741</v>
       </c>
       <c r="Q58">
-        <v>6.1465624728</v>
+        <v>6.1203403741</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1306553481929535</v>
+        <v>0.1324655886418295</v>
       </c>
       <c r="T58">
-        <v>1.95970781046082</v>
+        <v>2.001514749233939</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.80442638472499</v>
+        <v>4.720138202536832</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6199,22 +6199,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08312263311598669</v>
+        <v>0.08305347302707386</v>
       </c>
       <c r="C59">
-        <v>25.38419976185342</v>
+        <v>24.82836061368221</v>
       </c>
       <c r="D59">
-        <v>37.04829976185342</v>
+        <v>37.06376061368222</v>
       </c>
       <c r="E59">
-        <v>30.23410000000001</v>
+        <v>30.80540000000001</v>
       </c>
       <c r="F59">
-        <v>32.5641</v>
+        <v>33.1354</v>
       </c>
       <c r="G59">
         <v>20.9</v>
@@ -6235,28 +6235,28 @@
         <v>8.5</v>
       </c>
       <c r="M59">
-        <v>1.80079473</v>
+        <v>1.83238762</v>
       </c>
       <c r="N59">
-        <v>6.69920527</v>
+        <v>6.66761238</v>
       </c>
       <c r="O59">
-        <v>1.1388648959</v>
+        <v>1.1334941046</v>
       </c>
       <c r="P59">
-        <v>5.5603403741</v>
+        <v>5.534118275399999</v>
       </c>
       <c r="Q59">
-        <v>6.1203403741</v>
+        <v>6.0941182754</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1324655886418295</v>
+        <v>0.1343620310168425</v>
       </c>
       <c r="T59">
-        <v>2.001514749233939</v>
+        <v>2.045312494615301</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6273,7 +6273,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.720138202536832</v>
+        <v>4.638756509389644</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6281,22 +6281,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08305347302707387</v>
+        <v>0.08298431293816104</v>
       </c>
       <c r="C60">
-        <v>24.82836061368221</v>
+        <v>24.27253437502302</v>
       </c>
       <c r="D60">
-        <v>37.06376061368221</v>
+        <v>37.07923437502302</v>
       </c>
       <c r="E60">
-        <v>30.8054</v>
+        <v>31.3767</v>
       </c>
       <c r="F60">
-        <v>33.1354</v>
+        <v>33.7067</v>
       </c>
       <c r="G60">
         <v>20.9</v>
@@ -6317,28 +6317,28 @@
         <v>8.5</v>
       </c>
       <c r="M60">
-        <v>1.83238762</v>
+        <v>1.86398051</v>
       </c>
       <c r="N60">
-        <v>6.66761238</v>
+        <v>6.63601949</v>
       </c>
       <c r="O60">
-        <v>1.1334941046</v>
+        <v>1.1281233133</v>
       </c>
       <c r="P60">
-        <v>5.534118275399999</v>
+        <v>5.507896176699999</v>
       </c>
       <c r="Q60">
-        <v>6.0941182754</v>
+        <v>6.0678961767</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1343620310168425</v>
+        <v>0.1363509827760025</v>
       </c>
       <c r="T60">
-        <v>2.045312494615301</v>
+        <v>2.091246715381121</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.638756509389645</v>
+        <v>4.560133517705076</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6363,22 +6363,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08298431293816104</v>
+        <v>0.08416015284924822</v>
       </c>
       <c r="C61">
-        <v>24.27253437502302</v>
+        <v>23.43989907922301</v>
       </c>
       <c r="D61">
-        <v>37.07923437502302</v>
+        <v>36.81789907922301</v>
       </c>
       <c r="E61">
-        <v>31.3767</v>
+        <v>31.948</v>
       </c>
       <c r="F61">
-        <v>33.7067</v>
+        <v>34.278</v>
       </c>
       <c r="G61">
         <v>20.9</v>
@@ -6399,45 +6399,45 @@
         <v>8.5</v>
       </c>
       <c r="M61">
-        <v>1.86398051</v>
+        <v>1.9812684</v>
       </c>
       <c r="N61">
-        <v>6.63601949</v>
+        <v>6.5187316</v>
       </c>
       <c r="O61">
-        <v>1.1281233133</v>
+        <v>1.108184372</v>
       </c>
       <c r="P61">
-        <v>5.507896176699999</v>
+        <v>5.410547228</v>
       </c>
       <c r="Q61">
-        <v>6.0678961767</v>
+        <v>5.970547228</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1363509827760025</v>
+        <v>0.1384393821231205</v>
       </c>
       <c r="T61">
-        <v>2.091246715381121</v>
+        <v>2.139477647185231</v>
       </c>
       <c r="U61">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V61">
         <v>0.17</v>
       </c>
       <c r="W61">
-        <v>0.045899</v>
+        <v>0.047974</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>4.560133517705076</v>
+        <v>4.290180976994334</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6445,22 +6445,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08416015284924822</v>
+        <v>0.08411174276033537</v>
       </c>
       <c r="C62">
-        <v>23.43989907922301</v>
+        <v>22.87928569106918</v>
       </c>
       <c r="D62">
-        <v>36.81789907922301</v>
+        <v>36.82858569106918</v>
       </c>
       <c r="E62">
-        <v>31.948</v>
+        <v>32.5193</v>
       </c>
       <c r="F62">
-        <v>34.278</v>
+        <v>34.8493</v>
       </c>
       <c r="G62">
         <v>20.9</v>
@@ -6481,28 +6481,28 @@
         <v>8.5</v>
       </c>
       <c r="M62">
-        <v>1.9812684</v>
+        <v>2.01428954</v>
       </c>
       <c r="N62">
-        <v>6.5187316</v>
+        <v>6.48571046</v>
       </c>
       <c r="O62">
-        <v>1.108184372</v>
+        <v>1.1025707782</v>
       </c>
       <c r="P62">
-        <v>5.410547228</v>
+        <v>5.383139681799999</v>
       </c>
       <c r="Q62">
-        <v>5.970547228</v>
+        <v>5.9431396818</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1384393821231205</v>
+        <v>0.1406348788726548</v>
       </c>
       <c r="T62">
-        <v>2.139477647185231</v>
+        <v>2.190181960107501</v>
       </c>
       <c r="U62">
         <v>0.0578</v>
@@ -6519,7 +6519,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.290180976994334</v>
+        <v>4.219850141305901</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08411174276033537</v>
+        <v>0.08406333267142255</v>
       </c>
       <c r="C63">
-        <v>22.87928569106918</v>
+        <v>22.31867850842046</v>
       </c>
       <c r="D63">
-        <v>36.82858569106918</v>
+        <v>36.83927850842046</v>
       </c>
       <c r="E63">
-        <v>32.5193</v>
+        <v>33.0906</v>
       </c>
       <c r="F63">
-        <v>34.8493</v>
+        <v>35.4206</v>
       </c>
       <c r="G63">
         <v>20.9</v>
@@ -6563,28 +6563,28 @@
         <v>8.5</v>
       </c>
       <c r="M63">
-        <v>2.01428954</v>
+        <v>2.04731068</v>
       </c>
       <c r="N63">
-        <v>6.48571046</v>
+        <v>6.452689319999999</v>
       </c>
       <c r="O63">
-        <v>1.1025707782</v>
+        <v>1.0969571844</v>
       </c>
       <c r="P63">
-        <v>5.383139681799999</v>
+        <v>5.355732135599999</v>
       </c>
       <c r="Q63">
-        <v>5.9431396818</v>
+        <v>5.9157321356</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1406348788726548</v>
+        <v>0.1429459280826909</v>
       </c>
       <c r="T63">
-        <v>2.190181960107501</v>
+        <v>2.243554921078312</v>
       </c>
       <c r="U63">
         <v>0.0578</v>
@@ -6601,7 +6601,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.219850141305901</v>
+        <v>4.15178804225258</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6609,22 +6609,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08406333267142255</v>
+        <v>0.08401492258250971</v>
       </c>
       <c r="C64">
-        <v>22.31867850842046</v>
+        <v>21.75807753668357</v>
       </c>
       <c r="D64">
-        <v>36.83927850842046</v>
+        <v>36.84997753668356</v>
       </c>
       <c r="E64">
-        <v>33.0906</v>
+        <v>33.6619</v>
       </c>
       <c r="F64">
-        <v>35.4206</v>
+        <v>35.99189999999999</v>
       </c>
       <c r="G64">
         <v>20.9</v>
@@ -6645,28 +6645,28 @@
         <v>8.5</v>
       </c>
       <c r="M64">
-        <v>2.04731068</v>
+        <v>2.08033182</v>
       </c>
       <c r="N64">
-        <v>6.452689319999999</v>
+        <v>6.41966818</v>
       </c>
       <c r="O64">
-        <v>1.0969571844</v>
+        <v>1.0913435906</v>
       </c>
       <c r="P64">
-        <v>5.355732135599999</v>
+        <v>5.3283245894</v>
       </c>
       <c r="Q64">
-        <v>5.9157321356</v>
+        <v>5.888324589400001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1429459280826909</v>
+        <v>0.1453818988716479</v>
       </c>
       <c r="T64">
-        <v>2.243554921078312</v>
+        <v>2.299812906966463</v>
       </c>
       <c r="U64">
         <v>0.0578</v>
@@ -6683,7 +6683,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.15178804225258</v>
+        <v>4.085886644756509</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6691,22 +6691,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08401492258250971</v>
+        <v>0.08396651249359688</v>
       </c>
       <c r="C65">
-        <v>21.75807753668357</v>
+        <v>21.19748278127145</v>
       </c>
       <c r="D65">
-        <v>36.84997753668356</v>
+        <v>36.86068278127145</v>
       </c>
       <c r="E65">
-        <v>33.6619</v>
+        <v>34.2332</v>
       </c>
       <c r="F65">
-        <v>35.99189999999999</v>
+        <v>36.56319999999999</v>
       </c>
       <c r="G65">
         <v>20.9</v>
@@ -6727,28 +6727,28 @@
         <v>8.5</v>
       </c>
       <c r="M65">
-        <v>2.08033182</v>
+        <v>2.11335296</v>
       </c>
       <c r="N65">
-        <v>6.41966818</v>
+        <v>6.38664704</v>
       </c>
       <c r="O65">
-        <v>1.0913435906</v>
+        <v>1.0857299968</v>
       </c>
       <c r="P65">
-        <v>5.3283245894</v>
+        <v>5.3009170432</v>
       </c>
       <c r="Q65">
-        <v>5.888324589400001</v>
+        <v>5.860917043200001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1453818988716479</v>
+        <v>0.1479532013711024</v>
       </c>
       <c r="T65">
-        <v>2.299812906966463</v>
+        <v>2.359196336515068</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -6765,7 +6765,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.085886644756509</v>
+        <v>4.022044665932188</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6773,22 +6773,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08396651249359688</v>
+        <v>0.08580635240468407</v>
       </c>
       <c r="C66">
-        <v>21.19748278127145</v>
+        <v>20.22365284594068</v>
       </c>
       <c r="D66">
-        <v>36.86068278127145</v>
+        <v>36.45815284594068</v>
       </c>
       <c r="E66">
-        <v>34.2332</v>
+        <v>34.8045</v>
       </c>
       <c r="F66">
-        <v>36.56319999999999</v>
+        <v>37.1345</v>
       </c>
       <c r="G66">
         <v>20.9</v>
@@ -6809,45 +6809,45 @@
         <v>8.5</v>
       </c>
       <c r="M66">
-        <v>2.11335296</v>
+        <v>2.27634485</v>
       </c>
       <c r="N66">
-        <v>6.38664704</v>
+        <v>6.223655150000001</v>
       </c>
       <c r="O66">
-        <v>1.0857299968</v>
+        <v>1.0580213755</v>
       </c>
       <c r="P66">
-        <v>5.3009170432</v>
+        <v>5.165633774500001</v>
       </c>
       <c r="Q66">
-        <v>5.860917043200001</v>
+        <v>5.725633774500001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1479532013711024</v>
+        <v>0.1506714354419545</v>
       </c>
       <c r="T66">
-        <v>2.359196336515068</v>
+        <v>2.421973104895022</v>
       </c>
       <c r="U66">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V66">
         <v>0.17</v>
       </c>
       <c r="W66">
-        <v>0.047974</v>
+        <v>0.050879</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y66">
-        <v>4.022044665932188</v>
+        <v>3.734056375509186</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6855,22 +6855,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08580635240468407</v>
+        <v>0.08578699231577122</v>
       </c>
       <c r="C67">
-        <v>20.22365284594068</v>
+        <v>19.65654277518743</v>
       </c>
       <c r="D67">
-        <v>36.45815284594068</v>
+        <v>36.46234277518742</v>
       </c>
       <c r="E67">
-        <v>34.8045</v>
+        <v>35.3758</v>
       </c>
       <c r="F67">
-        <v>37.1345</v>
+        <v>37.7058</v>
       </c>
       <c r="G67">
         <v>20.9</v>
@@ -6891,28 +6891,28 @@
         <v>8.5</v>
       </c>
       <c r="M67">
-        <v>2.27634485</v>
+        <v>2.31136554</v>
       </c>
       <c r="N67">
-        <v>6.223655150000001</v>
+        <v>6.18863446</v>
       </c>
       <c r="O67">
-        <v>1.0580213755</v>
+        <v>1.0520678582</v>
       </c>
       <c r="P67">
-        <v>5.165633774500001</v>
+        <v>5.1365666018</v>
       </c>
       <c r="Q67">
-        <v>5.725633774500001</v>
+        <v>5.696566601800001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1506714354419545</v>
+        <v>0.1535495656346212</v>
       </c>
       <c r="T67">
-        <v>2.421973104895022</v>
+        <v>2.488442624356149</v>
       </c>
       <c r="U67">
         <v>0.0613</v>
@@ -6929,7 +6929,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.734056375509186</v>
+        <v>3.677479763759047</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6937,22 +6937,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08578699231577122</v>
+        <v>0.0857676322268584</v>
       </c>
       <c r="C68">
-        <v>19.65654277518743</v>
+        <v>19.08943366759458</v>
       </c>
       <c r="D68">
-        <v>36.46234277518742</v>
+        <v>36.46653366759458</v>
       </c>
       <c r="E68">
-        <v>35.3758</v>
+        <v>35.9471</v>
       </c>
       <c r="F68">
-        <v>37.7058</v>
+        <v>38.2771</v>
       </c>
       <c r="G68">
         <v>20.9</v>
@@ -6973,28 +6973,28 @@
         <v>8.5</v>
       </c>
       <c r="M68">
-        <v>2.31136554</v>
+        <v>2.34638623</v>
       </c>
       <c r="N68">
-        <v>6.18863446</v>
+        <v>6.15361377</v>
       </c>
       <c r="O68">
-        <v>1.0520678582</v>
+        <v>1.0461143409</v>
       </c>
       <c r="P68">
-        <v>5.1365666018</v>
+        <v>5.1074994291</v>
       </c>
       <c r="Q68">
-        <v>5.696566601800001</v>
+        <v>5.6674994291</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1535495656346212</v>
+        <v>0.156602127960177</v>
       </c>
       <c r="T68">
-        <v>2.488442624356149</v>
+        <v>2.558940599542193</v>
       </c>
       <c r="U68">
         <v>0.0613</v>
@@ -7011,7 +7011,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.677479763759047</v>
+        <v>3.622592006091001</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7019,22 +7019,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.0857676322268584</v>
+        <v>0.08574827213794556</v>
       </c>
       <c r="C69">
-        <v>19.08943366759458</v>
+        <v>18.52232552349431</v>
       </c>
       <c r="D69">
-        <v>36.46653366759458</v>
+        <v>36.47072552349431</v>
       </c>
       <c r="E69">
-        <v>35.9471</v>
+        <v>36.5184</v>
       </c>
       <c r="F69">
-        <v>38.2771</v>
+        <v>38.8484</v>
       </c>
       <c r="G69">
         <v>20.9</v>
@@ -7055,28 +7055,28 @@
         <v>8.5</v>
       </c>
       <c r="M69">
-        <v>2.34638623</v>
+        <v>2.38140692</v>
       </c>
       <c r="N69">
-        <v>6.15361377</v>
+        <v>6.11859308</v>
       </c>
       <c r="O69">
-        <v>1.0461143409</v>
+        <v>1.0401608236</v>
       </c>
       <c r="P69">
-        <v>5.1074994291</v>
+        <v>5.0784322564</v>
       </c>
       <c r="Q69">
-        <v>5.6674994291</v>
+        <v>5.638432256400001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.156602127960177</v>
+        <v>0.1598454754310799</v>
       </c>
       <c r="T69">
-        <v>2.558940599542193</v>
+        <v>2.633844698177365</v>
       </c>
       <c r="U69">
         <v>0.0613</v>
@@ -7093,7 +7093,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.622592006091001</v>
+        <v>3.569318594236722</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7101,22 +7101,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08574827213794556</v>
+        <v>0.08572891204903273</v>
       </c>
       <c r="C70">
-        <v>18.52232552349431</v>
+        <v>17.95521834321891</v>
       </c>
       <c r="D70">
-        <v>36.47072552349431</v>
+        <v>36.47491834321891</v>
       </c>
       <c r="E70">
-        <v>36.5184</v>
+        <v>37.0897</v>
       </c>
       <c r="F70">
-        <v>38.8484</v>
+        <v>39.4197</v>
       </c>
       <c r="G70">
         <v>20.9</v>
@@ -7137,28 +7137,28 @@
         <v>8.5</v>
       </c>
       <c r="M70">
-        <v>2.38140692</v>
+        <v>2.41642761</v>
       </c>
       <c r="N70">
-        <v>6.11859308</v>
+        <v>6.08357239</v>
       </c>
       <c r="O70">
-        <v>1.0401608236</v>
+        <v>1.0342073063</v>
       </c>
       <c r="P70">
-        <v>5.0784322564</v>
+        <v>5.049365083700001</v>
       </c>
       <c r="Q70">
-        <v>5.638432256400001</v>
+        <v>5.609365083700001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1598454754310799</v>
+        <v>0.163298071125912</v>
       </c>
       <c r="T70">
-        <v>2.633844698177365</v>
+        <v>2.713581319305128</v>
       </c>
       <c r="U70">
         <v>0.0613</v>
@@ -7175,7 +7175,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.569318594236722</v>
+        <v>3.517589339247783</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7183,22 +7183,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08572891204903273</v>
+        <v>0.08733635196011991</v>
       </c>
       <c r="C71">
-        <v>17.95521834321891</v>
+        <v>17.03904652450345</v>
       </c>
       <c r="D71">
-        <v>36.47491834321891</v>
+        <v>36.13004652450345</v>
       </c>
       <c r="E71">
-        <v>37.0897</v>
+        <v>37.661</v>
       </c>
       <c r="F71">
-        <v>39.4197</v>
+        <v>39.991</v>
       </c>
       <c r="G71">
         <v>20.9</v>
@@ -7219,45 +7219,45 @@
         <v>8.5</v>
       </c>
       <c r="M71">
-        <v>2.41642761</v>
+        <v>2.5634231</v>
       </c>
       <c r="N71">
-        <v>6.08357239</v>
+        <v>5.9365769</v>
       </c>
       <c r="O71">
-        <v>1.0342073063</v>
+        <v>1.009218073</v>
       </c>
       <c r="P71">
-        <v>5.049365083700001</v>
+        <v>4.927358827</v>
       </c>
       <c r="Q71">
-        <v>5.609365083700001</v>
+        <v>5.487358827</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.163298071125912</v>
+        <v>0.1669808398670664</v>
       </c>
       <c r="T71">
-        <v>2.713581319305128</v>
+        <v>2.798633715174743</v>
       </c>
       <c r="U71">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V71">
         <v>0.17</v>
       </c>
       <c r="W71">
-        <v>0.050879</v>
+        <v>0.053203</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y71">
-        <v>3.517589339247783</v>
+        <v>3.315878678006764</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7265,22 +7265,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08733635196011991</v>
+        <v>0.08734023187120707</v>
       </c>
       <c r="C72">
-        <v>17.03904652450345</v>
+        <v>16.46692198965667</v>
       </c>
       <c r="D72">
-        <v>36.13004652450345</v>
+        <v>36.12922198965667</v>
       </c>
       <c r="E72">
-        <v>37.661</v>
+        <v>38.2323</v>
       </c>
       <c r="F72">
-        <v>39.991</v>
+        <v>40.5623</v>
       </c>
       <c r="G72">
         <v>20.9</v>
@@ -7301,28 +7301,28 @@
         <v>8.5</v>
       </c>
       <c r="M72">
-        <v>2.5634231</v>
+        <v>2.60004343</v>
       </c>
       <c r="N72">
-        <v>5.9365769</v>
+        <v>5.89995657</v>
       </c>
       <c r="O72">
-        <v>1.009218073</v>
+        <v>1.0029926169</v>
       </c>
       <c r="P72">
-        <v>4.927358827</v>
+        <v>4.896963953099999</v>
       </c>
       <c r="Q72">
-        <v>5.487358827</v>
+        <v>5.4569639531</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1669808398670664</v>
+        <v>0.1709175926593348</v>
       </c>
       <c r="T72">
-        <v>2.798633715174743</v>
+        <v>2.889551793518124</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7339,7 +7339,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.315878678006764</v>
+        <v>3.269176161415118</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7347,22 +7347,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08734023187120707</v>
+        <v>0.08734411178229423</v>
       </c>
       <c r="C73">
-        <v>16.46692198965668</v>
+        <v>15.89479749244296</v>
       </c>
       <c r="D73">
-        <v>36.12922198965667</v>
+        <v>36.12839749244296</v>
       </c>
       <c r="E73">
-        <v>38.2323</v>
+        <v>38.8036</v>
       </c>
       <c r="F73">
-        <v>40.56229999999999</v>
+        <v>41.13359999999999</v>
       </c>
       <c r="G73">
         <v>20.9</v>
@@ -7383,28 +7383,28 @@
         <v>8.5</v>
       </c>
       <c r="M73">
-        <v>2.60004343</v>
+        <v>2.63666376</v>
       </c>
       <c r="N73">
-        <v>5.899956570000001</v>
+        <v>5.863336240000001</v>
       </c>
       <c r="O73">
-        <v>1.0029926169</v>
+        <v>0.9967671608000002</v>
       </c>
       <c r="P73">
-        <v>4.8969639531</v>
+        <v>4.8665690792</v>
       </c>
       <c r="Q73">
-        <v>5.456963953100001</v>
+        <v>5.426569079200001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1709175926593347</v>
+        <v>0.1751355420796223</v>
       </c>
       <c r="T73">
-        <v>2.889551793518123</v>
+        <v>2.986964020314602</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.269176161415119</v>
+        <v>3.223770936951021</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7429,22 +7429,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08734411178229423</v>
+        <v>0.08734799169338141</v>
       </c>
       <c r="C74">
-        <v>15.89479749244296</v>
+        <v>15.32267303285973</v>
       </c>
       <c r="D74">
-        <v>36.12839749244296</v>
+        <v>36.12757303285973</v>
       </c>
       <c r="E74">
-        <v>38.8036</v>
+        <v>39.3749</v>
       </c>
       <c r="F74">
-        <v>41.13359999999999</v>
+        <v>41.70489999999999</v>
       </c>
       <c r="G74">
         <v>20.9</v>
@@ -7465,28 +7465,28 @@
         <v>8.5</v>
       </c>
       <c r="M74">
-        <v>2.63666376</v>
+        <v>2.67328409</v>
       </c>
       <c r="N74">
-        <v>5.863336240000001</v>
+        <v>5.826715910000001</v>
       </c>
       <c r="O74">
-        <v>0.9967671608000002</v>
+        <v>0.9905417047000002</v>
       </c>
       <c r="P74">
-        <v>4.8665690792</v>
+        <v>4.836174205300001</v>
       </c>
       <c r="Q74">
-        <v>5.426569079200001</v>
+        <v>5.396174205300001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1751355420796223</v>
+        <v>0.1796659321977089</v>
       </c>
       <c r="T74">
-        <v>2.986964020314602</v>
+        <v>3.091591967614524</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.223770936951021</v>
+        <v>3.179609691239363</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7511,22 +7511,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08734799169338141</v>
+        <v>0.08735187160446858</v>
       </c>
       <c r="C75">
-        <v>15.32267303285973</v>
+        <v>14.75054861090442</v>
       </c>
       <c r="D75">
-        <v>36.12757303285973</v>
+        <v>36.12674861090442</v>
       </c>
       <c r="E75">
-        <v>39.3749</v>
+        <v>39.9462</v>
       </c>
       <c r="F75">
-        <v>41.70489999999999</v>
+        <v>42.2762</v>
       </c>
       <c r="G75">
         <v>20.9</v>
@@ -7547,28 +7547,28 @@
         <v>8.5</v>
       </c>
       <c r="M75">
-        <v>2.67328409</v>
+        <v>2.70990442</v>
       </c>
       <c r="N75">
-        <v>5.826715910000001</v>
+        <v>5.79009558</v>
       </c>
       <c r="O75">
-        <v>0.9905417047000002</v>
+        <v>0.9843162486000001</v>
       </c>
       <c r="P75">
-        <v>4.836174205300001</v>
+        <v>4.8057793314</v>
       </c>
       <c r="Q75">
-        <v>5.396174205300001</v>
+        <v>5.365779331400001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1796659321977089</v>
+        <v>0.1845448138633407</v>
       </c>
       <c r="T75">
-        <v>3.091591967614524</v>
+        <v>3.204268218552902</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7585,7 +7585,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.179609691239363</v>
+        <v>3.136641992709101</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7593,22 +7593,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08735187160446858</v>
+        <v>0.08735575151555575</v>
       </c>
       <c r="C76">
-        <v>14.75054861090442</v>
+        <v>14.17842422657445</v>
       </c>
       <c r="D76">
-        <v>36.12674861090442</v>
+        <v>36.12592422657445</v>
       </c>
       <c r="E76">
-        <v>39.9462</v>
+        <v>40.5175</v>
       </c>
       <c r="F76">
-        <v>42.2762</v>
+        <v>42.8475</v>
       </c>
       <c r="G76">
         <v>20.9</v>
@@ -7629,28 +7629,28 @@
         <v>8.5</v>
       </c>
       <c r="M76">
-        <v>2.70990442</v>
+        <v>2.74652475</v>
       </c>
       <c r="N76">
-        <v>5.79009558</v>
+        <v>5.75347525</v>
       </c>
       <c r="O76">
-        <v>0.9843162486000001</v>
+        <v>0.9780907925000001</v>
       </c>
       <c r="P76">
-        <v>4.8057793314</v>
+        <v>4.7753844575</v>
       </c>
       <c r="Q76">
-        <v>5.365779331400001</v>
+        <v>5.335384457500001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1845448138633407</v>
+        <v>0.189814006062223</v>
       </c>
       <c r="T76">
-        <v>3.204268218552902</v>
+        <v>3.32595856956635</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7667,7 +7667,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.136641992709101</v>
+        <v>3.09482009947298</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7675,22 +7675,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08735575151555575</v>
+        <v>0.08735963142664292</v>
       </c>
       <c r="C77">
-        <v>14.17842422657445</v>
+        <v>13.60629987986723</v>
       </c>
       <c r="D77">
-        <v>36.12592422657445</v>
+        <v>36.12509987986723</v>
       </c>
       <c r="E77">
-        <v>40.5175</v>
+        <v>41.0888</v>
       </c>
       <c r="F77">
-        <v>42.8475</v>
+        <v>43.4188</v>
       </c>
       <c r="G77">
         <v>20.9</v>
@@ -7711,28 +7711,28 @@
         <v>8.5</v>
       </c>
       <c r="M77">
-        <v>2.74652475</v>
+        <v>2.78314508</v>
       </c>
       <c r="N77">
-        <v>5.75347525</v>
+        <v>5.716854919999999</v>
       </c>
       <c r="O77">
-        <v>0.9780907925000001</v>
+        <v>0.9718653363999999</v>
       </c>
       <c r="P77">
-        <v>4.7753844575</v>
+        <v>4.7449895836</v>
       </c>
       <c r="Q77">
-        <v>5.335384457500001</v>
+        <v>5.3049895836</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.189814006062223</v>
+        <v>0.1955222976110122</v>
       </c>
       <c r="T77">
-        <v>3.32595856956635</v>
+        <v>3.457789783164253</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7749,7 +7749,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.09482009947298</v>
+        <v>3.054098782374651</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7757,22 +7757,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08735963142664292</v>
+        <v>0.08736351133773007</v>
       </c>
       <c r="C78">
-        <v>13.60629987986723</v>
+        <v>13.03417557078021</v>
       </c>
       <c r="D78">
-        <v>36.12509987986723</v>
+        <v>36.12427557078021</v>
       </c>
       <c r="E78">
-        <v>41.0888</v>
+        <v>41.6601</v>
       </c>
       <c r="F78">
-        <v>43.4188</v>
+        <v>43.9901</v>
       </c>
       <c r="G78">
         <v>20.9</v>
@@ -7793,28 +7793,28 @@
         <v>8.5</v>
       </c>
       <c r="M78">
-        <v>2.78314508</v>
+        <v>2.81976541</v>
       </c>
       <c r="N78">
-        <v>5.716854919999999</v>
+        <v>5.68023459</v>
       </c>
       <c r="O78">
-        <v>0.9718653363999999</v>
+        <v>0.9656398803</v>
       </c>
       <c r="P78">
-        <v>4.7449895836</v>
+        <v>4.714594709699999</v>
       </c>
       <c r="Q78">
-        <v>5.3049895836</v>
+        <v>5.2745947097</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1955222976110122</v>
+        <v>0.2017269623379569</v>
       </c>
       <c r="T78">
-        <v>3.457789783164253</v>
+        <v>3.601084580553277</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7831,7 +7831,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.054098782374651</v>
+        <v>3.014435161824331</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7839,22 +7839,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08736351133773007</v>
+        <v>0.09241711124881725</v>
       </c>
       <c r="C79">
-        <v>13.03417557078021</v>
+        <v>11.42022259749228</v>
       </c>
       <c r="D79">
-        <v>36.12427557078021</v>
+        <v>35.08162259749228</v>
       </c>
       <c r="E79">
-        <v>41.6601</v>
+        <v>42.2314</v>
       </c>
       <c r="F79">
-        <v>43.9901</v>
+        <v>44.5614</v>
       </c>
       <c r="G79">
         <v>20.9</v>
@@ -7875,45 +7875,45 @@
         <v>8.5</v>
       </c>
       <c r="M79">
-        <v>2.81976541</v>
+        <v>3.20396466</v>
       </c>
       <c r="N79">
-        <v>5.68023459</v>
+        <v>5.29603534</v>
       </c>
       <c r="O79">
-        <v>0.9656398803</v>
+        <v>0.9003260077999999</v>
       </c>
       <c r="P79">
-        <v>4.714594709699999</v>
+        <v>4.395709332199999</v>
       </c>
       <c r="Q79">
-        <v>5.2745947097</v>
+        <v>4.9557093322</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2017269623379569</v>
+        <v>0.2084956874946239</v>
       </c>
       <c r="T79">
-        <v>3.601084580553277</v>
+        <v>3.75740617770494</v>
       </c>
       <c r="U79">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V79">
         <v>0.17</v>
       </c>
       <c r="W79">
-        <v>0.053203</v>
+        <v>0.059677</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y79">
-        <v>3.014435161824331</v>
+        <v>2.652963094792687</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7921,22 +7921,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09241711124881725</v>
+        <v>0.09248573115990442</v>
       </c>
       <c r="C80">
-        <v>11.42022259749228</v>
+        <v>10.83517903144269</v>
       </c>
       <c r="D80">
-        <v>35.08162259749228</v>
+        <v>35.06787903144269</v>
       </c>
       <c r="E80">
-        <v>42.2314</v>
+        <v>42.8027</v>
       </c>
       <c r="F80">
-        <v>44.5614</v>
+        <v>45.1327</v>
       </c>
       <c r="G80">
         <v>20.9</v>
@@ -7957,28 +7957,28 @@
         <v>8.5</v>
       </c>
       <c r="M80">
-        <v>3.20396466</v>
+        <v>3.24504113</v>
       </c>
       <c r="N80">
-        <v>5.29603534</v>
+        <v>5.254958869999999</v>
       </c>
       <c r="O80">
-        <v>0.9003260077999999</v>
+        <v>0.8933430079</v>
       </c>
       <c r="P80">
-        <v>4.395709332199999</v>
+        <v>4.361615862099999</v>
       </c>
       <c r="Q80">
-        <v>4.9557093322</v>
+        <v>4.921615862099999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2084956874946239</v>
+        <v>0.215909053142402</v>
       </c>
       <c r="T80">
-        <v>3.75740617770494</v>
+        <v>3.928615546013904</v>
       </c>
       <c r="U80">
         <v>0.07190000000000001</v>
@@ -7995,7 +7995,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.652963094792687</v>
+        <v>2.619381283466197</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8003,22 +8003,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09248573115990442</v>
+        <v>0.09255435107099158</v>
       </c>
       <c r="C81">
-        <v>10.83517903144269</v>
+        <v>10.25014622952684</v>
       </c>
       <c r="D81">
-        <v>35.06787903144269</v>
+        <v>35.05414622952684</v>
       </c>
       <c r="E81">
-        <v>42.8027</v>
+        <v>43.374</v>
       </c>
       <c r="F81">
-        <v>45.1327</v>
+        <v>45.704</v>
       </c>
       <c r="G81">
         <v>20.9</v>
@@ -8039,28 +8039,28 @@
         <v>8.5</v>
       </c>
       <c r="M81">
-        <v>3.24504113</v>
+        <v>3.2861176</v>
       </c>
       <c r="N81">
-        <v>5.254958869999999</v>
+        <v>5.213882399999999</v>
       </c>
       <c r="O81">
-        <v>0.8933430079</v>
+        <v>0.8863600079999999</v>
       </c>
       <c r="P81">
-        <v>4.361615862099999</v>
+        <v>4.327522392</v>
       </c>
       <c r="Q81">
-        <v>4.921615862099999</v>
+        <v>4.887522392</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.215909053142402</v>
+        <v>0.224063755354958</v>
       </c>
       <c r="T81">
-        <v>3.928615546013904</v>
+        <v>4.116945851153764</v>
       </c>
       <c r="U81">
         <v>0.07190000000000001</v>
@@ -8077,7 +8077,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.619381283466197</v>
+        <v>2.58663901742287</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8085,22 +8085,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09255435107099158</v>
+        <v>0.09262297098207876</v>
       </c>
       <c r="C82">
-        <v>10.25014622952684</v>
+        <v>9.665124179103785</v>
       </c>
       <c r="D82">
-        <v>35.05414622952684</v>
+        <v>35.04042417910379</v>
       </c>
       <c r="E82">
-        <v>43.374</v>
+        <v>43.9453</v>
       </c>
       <c r="F82">
-        <v>45.704</v>
+        <v>46.2753</v>
       </c>
       <c r="G82">
         <v>20.9</v>
@@ -8121,28 +8121,28 @@
         <v>8.5</v>
       </c>
       <c r="M82">
-        <v>3.2861176</v>
+        <v>3.32719407</v>
       </c>
       <c r="N82">
-        <v>5.213882399999999</v>
+        <v>5.172805929999999</v>
       </c>
       <c r="O82">
-        <v>0.8863600079999999</v>
+        <v>0.8793770080999999</v>
       </c>
       <c r="P82">
-        <v>4.327522392</v>
+        <v>4.293428921899999</v>
       </c>
       <c r="Q82">
-        <v>4.887522392</v>
+        <v>4.8534289219</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.224063755354958</v>
+        <v>0.2330768472740988</v>
       </c>
       <c r="T82">
-        <v>4.116945851153764</v>
+        <v>4.325100398939926</v>
       </c>
       <c r="U82">
         <v>0.07190000000000001</v>
@@ -8159,7 +8159,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.58663901742287</v>
+        <v>2.554705202392958</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8167,22 +8167,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09262297098207876</v>
+        <v>0.09269159089316592</v>
       </c>
       <c r="C83">
-        <v>9.665124179103785</v>
+        <v>9.080112867552366</v>
       </c>
       <c r="D83">
-        <v>35.04042417910379</v>
+        <v>35.02671286755237</v>
       </c>
       <c r="E83">
-        <v>43.9453</v>
+        <v>44.5166</v>
       </c>
       <c r="F83">
-        <v>46.2753</v>
+        <v>46.8466</v>
       </c>
       <c r="G83">
         <v>20.9</v>
@@ -8203,28 +8203,28 @@
         <v>8.5</v>
       </c>
       <c r="M83">
-        <v>3.32719407</v>
+        <v>3.368270540000001</v>
       </c>
       <c r="N83">
-        <v>5.172805929999999</v>
+        <v>5.131729459999999</v>
       </c>
       <c r="O83">
-        <v>0.8793770080999999</v>
+        <v>0.8723940081999999</v>
       </c>
       <c r="P83">
-        <v>4.293428921899999</v>
+        <v>4.259335451799999</v>
       </c>
       <c r="Q83">
-        <v>4.8534289219</v>
+        <v>4.8193354518</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2330768472740988</v>
+        <v>0.2430913938509219</v>
       </c>
       <c r="T83">
-        <v>4.325100398939926</v>
+        <v>4.556383229813439</v>
       </c>
       <c r="U83">
         <v>0.07190000000000001</v>
@@ -8241,7 +8241,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.554705202392958</v>
+        <v>2.52355026090036</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8249,22 +8249,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09269159089316592</v>
+        <v>0.09544692080425309</v>
       </c>
       <c r="C84">
-        <v>9.080112867552366</v>
+        <v>7.966984331813514</v>
       </c>
       <c r="D84">
-        <v>35.02671286755237</v>
+        <v>34.48488433181352</v>
       </c>
       <c r="E84">
-        <v>44.5166</v>
+        <v>45.0879</v>
       </c>
       <c r="F84">
-        <v>46.8466</v>
+        <v>47.4179</v>
       </c>
       <c r="G84">
         <v>20.9</v>
@@ -8285,45 +8285,45 @@
         <v>8.5</v>
       </c>
       <c r="M84">
-        <v>3.368270540000001</v>
+        <v>3.594276820000001</v>
       </c>
       <c r="N84">
-        <v>5.131729459999999</v>
+        <v>4.905723179999999</v>
       </c>
       <c r="O84">
-        <v>0.8723940081999999</v>
+        <v>0.8339729405999999</v>
       </c>
       <c r="P84">
-        <v>4.259335451799999</v>
+        <v>4.071750239399999</v>
       </c>
       <c r="Q84">
-        <v>4.8193354518</v>
+        <v>4.6317502394</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2430913938509219</v>
+        <v>0.2542841223779594</v>
       </c>
       <c r="T84">
-        <v>4.556383229813439</v>
+        <v>4.8148758054956</v>
       </c>
       <c r="U84">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V84">
         <v>0.17</v>
       </c>
       <c r="W84">
-        <v>0.059677</v>
+        <v>0.062914</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y84">
-        <v>2.52355026090036</v>
+        <v>2.364870716885963</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8331,22 +8331,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09544692080425309</v>
+        <v>0.09554791071534027</v>
       </c>
       <c r="C85">
-        <v>7.966984331813514</v>
+        <v>7.376143210445854</v>
       </c>
       <c r="D85">
-        <v>34.48488433181352</v>
+        <v>34.46534321044586</v>
       </c>
       <c r="E85">
-        <v>45.0879</v>
+        <v>45.65920000000001</v>
       </c>
       <c r="F85">
-        <v>47.4179</v>
+        <v>47.9892</v>
       </c>
       <c r="G85">
         <v>20.9</v>
@@ -8367,28 +8367,28 @@
         <v>8.5</v>
       </c>
       <c r="M85">
-        <v>3.594276820000001</v>
+        <v>3.63758136</v>
       </c>
       <c r="N85">
-        <v>4.905723179999999</v>
+        <v>4.86241864</v>
       </c>
       <c r="O85">
-        <v>0.8339729405999999</v>
+        <v>0.8266111688</v>
       </c>
       <c r="P85">
-        <v>4.071750239399999</v>
+        <v>4.0358074712</v>
       </c>
       <c r="Q85">
-        <v>4.6317502394</v>
+        <v>4.595807471200001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2542841223779594</v>
+        <v>0.2668759419708768</v>
       </c>
       <c r="T85">
-        <v>4.8148758054956</v>
+        <v>5.105679953138033</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8405,7 +8405,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.364870716885963</v>
+        <v>2.336717494065892</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8413,22 +8413,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09554791071534027</v>
+        <v>0.09564890062642743</v>
       </c>
       <c r="C86">
-        <v>7.376143210445861</v>
+        <v>6.78532422278537</v>
       </c>
       <c r="D86">
-        <v>34.46534321044586</v>
+        <v>34.44582422278537</v>
       </c>
       <c r="E86">
-        <v>45.6592</v>
+        <v>46.2305</v>
       </c>
       <c r="F86">
-        <v>47.9892</v>
+        <v>48.5605</v>
       </c>
       <c r="G86">
         <v>20.9</v>
@@ -8449,28 +8449,28 @@
         <v>8.5</v>
       </c>
       <c r="M86">
-        <v>3.63758136</v>
+        <v>3.6808859</v>
       </c>
       <c r="N86">
-        <v>4.86241864</v>
+        <v>4.8191141</v>
       </c>
       <c r="O86">
-        <v>0.8266111688</v>
+        <v>0.8192493970000001</v>
       </c>
       <c r="P86">
-        <v>4.0358074712</v>
+        <v>3.999864703</v>
       </c>
       <c r="Q86">
-        <v>4.595807471200001</v>
+        <v>4.559864703000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2668759419708767</v>
+        <v>0.2811466708428496</v>
       </c>
       <c r="T86">
-        <v>5.105679953138029</v>
+        <v>5.435257987132784</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.336717494065892</v>
+        <v>2.309226700018058</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8495,22 +8495,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09564890062642743</v>
+        <v>0.09574989053751461</v>
       </c>
       <c r="C87">
-        <v>6.78532422278537</v>
+        <v>6.194527331247933</v>
       </c>
       <c r="D87">
-        <v>34.44582422278537</v>
+        <v>34.42632733124793</v>
       </c>
       <c r="E87">
-        <v>46.2305</v>
+        <v>46.8018</v>
       </c>
       <c r="F87">
-        <v>48.5605</v>
+        <v>49.1318</v>
       </c>
       <c r="G87">
         <v>20.9</v>
@@ -8531,28 +8531,28 @@
         <v>8.5</v>
       </c>
       <c r="M87">
-        <v>3.6808859</v>
+        <v>3.72419044</v>
       </c>
       <c r="N87">
-        <v>4.8191141</v>
+        <v>4.77580956</v>
       </c>
       <c r="O87">
-        <v>0.8192493970000001</v>
+        <v>0.8118876252</v>
       </c>
       <c r="P87">
-        <v>3.999864703</v>
+        <v>3.9639219348</v>
       </c>
       <c r="Q87">
-        <v>4.559864703000001</v>
+        <v>4.523921934800001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2811466708428496</v>
+        <v>0.2974560752679615</v>
       </c>
       <c r="T87">
-        <v>5.435257987132784</v>
+        <v>5.811918597412506</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.309226700018058</v>
+        <v>2.282375226762034</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8577,22 +8577,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09574989053751461</v>
+        <v>0.09585088044860177</v>
       </c>
       <c r="C88">
-        <v>6.194527331247933</v>
+        <v>5.60375249833448</v>
       </c>
       <c r="D88">
-        <v>34.42632733124793</v>
+        <v>34.40685249833448</v>
       </c>
       <c r="E88">
-        <v>46.8018</v>
+        <v>47.3731</v>
       </c>
       <c r="F88">
-        <v>49.1318</v>
+        <v>49.7031</v>
       </c>
       <c r="G88">
         <v>20.9</v>
@@ -8613,28 +8613,28 @@
         <v>8.5</v>
       </c>
       <c r="M88">
-        <v>3.72419044</v>
+        <v>3.76749498</v>
       </c>
       <c r="N88">
-        <v>4.77580956</v>
+        <v>4.73250502</v>
       </c>
       <c r="O88">
-        <v>0.8118876252</v>
+        <v>0.8045258534</v>
       </c>
       <c r="P88">
-        <v>3.9639219348</v>
+        <v>3.9279791666</v>
       </c>
       <c r="Q88">
-        <v>4.523921934800001</v>
+        <v>4.487979166600001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2974560752679615</v>
+        <v>0.3162746188353983</v>
       </c>
       <c r="T88">
-        <v>5.811918597412506</v>
+        <v>6.246526993889106</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8651,7 +8651,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.282375226762034</v>
+        <v>2.256141028753275</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8659,22 +8659,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09585088044860177</v>
+        <v>0.09595187035968895</v>
       </c>
       <c r="C89">
-        <v>5.60375249833448</v>
+        <v>5.012999686630778</v>
       </c>
       <c r="D89">
-        <v>34.40685249833448</v>
+        <v>34.38739968663077</v>
       </c>
       <c r="E89">
-        <v>47.3731</v>
+        <v>47.94439999999999</v>
       </c>
       <c r="F89">
-        <v>49.7031</v>
+        <v>50.27439999999999</v>
       </c>
       <c r="G89">
         <v>20.9</v>
@@ -8695,28 +8695,28 @@
         <v>8.5</v>
       </c>
       <c r="M89">
-        <v>3.76749498</v>
+        <v>3.81079952</v>
       </c>
       <c r="N89">
-        <v>4.73250502</v>
+        <v>4.68920048</v>
       </c>
       <c r="O89">
-        <v>0.8045258534</v>
+        <v>0.7971640816000001</v>
       </c>
       <c r="P89">
-        <v>3.9279791666</v>
+        <v>3.8920363984</v>
       </c>
       <c r="Q89">
-        <v>4.487979166600001</v>
+        <v>4.452036398400001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3162746188353983</v>
+        <v>0.3382295863307413</v>
       </c>
       <c r="T89">
-        <v>6.246526993889106</v>
+        <v>6.753570123111808</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8733,7 +8733,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.256141028753275</v>
+        <v>2.230503062517442</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8741,22 +8741,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09595187035968895</v>
+        <v>0.09605286027077611</v>
       </c>
       <c r="C90">
-        <v>5.012999686630778</v>
+        <v>4.422268858807108</v>
       </c>
       <c r="D90">
-        <v>34.38739968663077</v>
+        <v>34.3679688588071</v>
       </c>
       <c r="E90">
-        <v>47.94439999999999</v>
+        <v>48.5157</v>
       </c>
       <c r="F90">
-        <v>50.27439999999999</v>
+        <v>50.84569999999999</v>
       </c>
       <c r="G90">
         <v>20.9</v>
@@ -8777,28 +8777,28 @@
         <v>8.5</v>
       </c>
       <c r="M90">
-        <v>3.81079952</v>
+        <v>3.85410406</v>
       </c>
       <c r="N90">
-        <v>4.68920048</v>
+        <v>4.64589594</v>
       </c>
       <c r="O90">
-        <v>0.7971640816000001</v>
+        <v>0.7898023098000001</v>
       </c>
       <c r="P90">
-        <v>3.8920363984</v>
+        <v>3.8560936302</v>
       </c>
       <c r="Q90">
-        <v>4.452036398400001</v>
+        <v>4.416093630200001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3382295863307413</v>
+        <v>0.3641763660979647</v>
       </c>
       <c r="T90">
-        <v>6.753570123111808</v>
+        <v>7.352802912193181</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8815,7 +8815,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.230503062517442</v>
+        <v>2.205441230354325</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8823,22 +8823,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09605286027077611</v>
+        <v>0.09615385018186329</v>
       </c>
       <c r="C91">
-        <v>4.422268858807108</v>
+        <v>3.831559977618127</v>
       </c>
       <c r="D91">
-        <v>34.3679688588071</v>
+        <v>34.34855997761812</v>
       </c>
       <c r="E91">
-        <v>48.5157</v>
+        <v>49.087</v>
       </c>
       <c r="F91">
-        <v>50.84569999999999</v>
+        <v>51.41699999999999</v>
       </c>
       <c r="G91">
         <v>20.9</v>
@@ -8859,28 +8859,28 @@
         <v>8.5</v>
       </c>
       <c r="M91">
-        <v>3.85410406</v>
+        <v>3.8974086</v>
       </c>
       <c r="N91">
-        <v>4.64589594</v>
+        <v>4.6025914</v>
       </c>
       <c r="O91">
-        <v>0.7898023098000001</v>
+        <v>0.782440538</v>
       </c>
       <c r="P91">
-        <v>3.8560936302</v>
+        <v>3.820150862</v>
       </c>
       <c r="Q91">
-        <v>4.416093630200001</v>
+        <v>4.380150862000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3641763660979647</v>
+        <v>0.395312501818633</v>
       </c>
       <c r="T91">
-        <v>7.352802912193181</v>
+        <v>8.071882259090831</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8897,7 +8897,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.205441230354325</v>
+        <v>2.180936327794833</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8905,22 +8905,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09615385018186329</v>
+        <v>0.09625484009295046</v>
       </c>
       <c r="C92">
-        <v>3.831559977618127</v>
+        <v>3.240873005902543</v>
       </c>
       <c r="D92">
-        <v>34.34855997761812</v>
+        <v>34.32917300590254</v>
       </c>
       <c r="E92">
-        <v>49.087</v>
+        <v>49.6583</v>
       </c>
       <c r="F92">
-        <v>51.41699999999999</v>
+        <v>51.9883</v>
       </c>
       <c r="G92">
         <v>20.9</v>
@@ -8941,28 +8941,28 @@
         <v>8.5</v>
       </c>
       <c r="M92">
-        <v>3.8974086</v>
+        <v>3.94071314</v>
       </c>
       <c r="N92">
-        <v>4.6025914</v>
+        <v>4.55928686</v>
       </c>
       <c r="O92">
-        <v>0.782440538</v>
+        <v>0.7750787662000002</v>
       </c>
       <c r="P92">
-        <v>3.820150862</v>
+        <v>3.7842080938</v>
       </c>
       <c r="Q92">
-        <v>4.380150862000001</v>
+        <v>4.344208093800001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.395312501818633</v>
+        <v>0.4333677788105608</v>
       </c>
       <c r="T92">
-        <v>8.071882259090831</v>
+        <v>8.950757016410179</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8979,7 +8979,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.180936327794833</v>
+        <v>2.156969994522362</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8987,22 +8987,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09625484009295046</v>
+        <v>0.09635583000403762</v>
       </c>
       <c r="C93">
-        <v>3.240873005902543</v>
+        <v>2.650207906582942</v>
       </c>
       <c r="D93">
-        <v>34.32917300590254</v>
+        <v>34.30980790658294</v>
       </c>
       <c r="E93">
-        <v>49.6583</v>
+        <v>50.2296</v>
       </c>
       <c r="F93">
-        <v>51.9883</v>
+        <v>52.5596</v>
       </c>
       <c r="G93">
         <v>20.9</v>
@@ -9023,28 +9023,28 @@
         <v>8.5</v>
       </c>
       <c r="M93">
-        <v>3.94071314</v>
+        <v>3.98401768</v>
       </c>
       <c r="N93">
-        <v>4.55928686</v>
+        <v>4.51598232</v>
       </c>
       <c r="O93">
-        <v>0.7750787662000002</v>
+        <v>0.7677169944000001</v>
       </c>
       <c r="P93">
-        <v>3.7842080938</v>
+        <v>3.7482653256</v>
       </c>
       <c r="Q93">
-        <v>4.344208093800001</v>
+        <v>4.308265325600001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4333677788105608</v>
+        <v>0.4809368750504705</v>
       </c>
       <c r="T93">
-        <v>8.950757016410179</v>
+        <v>10.04935046305937</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -9061,7 +9061,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.156969994522362</v>
+        <v>2.133524668494945</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9069,22 +9069,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09635583000403762</v>
+        <v>0.09645681991512478</v>
       </c>
       <c r="C94">
-        <v>2.650207906582942</v>
+        <v>2.059564642665507</v>
       </c>
       <c r="D94">
-        <v>34.30980790658294</v>
+        <v>34.2904646426655</v>
       </c>
       <c r="E94">
-        <v>50.2296</v>
+        <v>50.8009</v>
       </c>
       <c r="F94">
-        <v>52.5596</v>
+        <v>53.1309</v>
       </c>
       <c r="G94">
         <v>20.9</v>
@@ -9105,28 +9105,28 @@
         <v>8.5</v>
       </c>
       <c r="M94">
-        <v>3.98401768</v>
+        <v>4.02732222</v>
       </c>
       <c r="N94">
-        <v>4.51598232</v>
+        <v>4.47267778</v>
       </c>
       <c r="O94">
-        <v>0.7677169944000001</v>
+        <v>0.7603552226</v>
       </c>
       <c r="P94">
-        <v>3.7482653256</v>
+        <v>3.7123225574</v>
       </c>
       <c r="Q94">
-        <v>4.308265325600001</v>
+        <v>4.272322557400001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4809368750504705</v>
+        <v>0.5420971416446402</v>
       </c>
       <c r="T94">
-        <v>10.04935046305937</v>
+        <v>11.46182775160832</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9143,7 +9143,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.133524668494945</v>
+        <v>2.110583543027257</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9151,22 +9151,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09645681991512478</v>
+        <v>0.09655780982621195</v>
       </c>
       <c r="C95">
-        <v>2.059564642665507</v>
+        <v>1.468943177239794</v>
       </c>
       <c r="D95">
-        <v>34.2904646426655</v>
+        <v>34.27114317723979</v>
       </c>
       <c r="E95">
-        <v>50.8009</v>
+        <v>51.3722</v>
       </c>
       <c r="F95">
-        <v>53.1309</v>
+        <v>53.7022</v>
       </c>
       <c r="G95">
         <v>20.9</v>
@@ -9187,28 +9187,28 @@
         <v>8.5</v>
       </c>
       <c r="M95">
-        <v>4.02732222</v>
+        <v>4.070626760000001</v>
       </c>
       <c r="N95">
-        <v>4.47267778</v>
+        <v>4.429373239999999</v>
       </c>
       <c r="O95">
-        <v>0.7603552226</v>
+        <v>0.7529934507999999</v>
       </c>
       <c r="P95">
-        <v>3.7123225574</v>
+        <v>3.676379789199999</v>
       </c>
       <c r="Q95">
-        <v>4.272322557400001</v>
+        <v>4.2363797892</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5420971416446402</v>
+        <v>0.6236441637701999</v>
       </c>
       <c r="T95">
-        <v>11.46182775160832</v>
+        <v>13.34513080300693</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9225,7 +9225,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.110583543027257</v>
+        <v>2.088130526612074</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9233,22 +9233,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09655780982621195</v>
+        <v>0.09665879973729913</v>
       </c>
       <c r="C96">
-        <v>1.468943177239794</v>
+        <v>0.8783434734785303</v>
       </c>
       <c r="D96">
-        <v>34.27114317723979</v>
+        <v>34.25184347347853</v>
       </c>
       <c r="E96">
-        <v>51.3722</v>
+        <v>51.9435</v>
       </c>
       <c r="F96">
-        <v>53.7022</v>
+        <v>54.2735</v>
       </c>
       <c r="G96">
         <v>20.9</v>
@@ -9269,28 +9269,28 @@
         <v>8.5</v>
       </c>
       <c r="M96">
-        <v>4.070626760000001</v>
+        <v>4.1139313</v>
       </c>
       <c r="N96">
-        <v>4.429373239999999</v>
+        <v>4.3860687</v>
       </c>
       <c r="O96">
-        <v>0.7529934507999999</v>
+        <v>0.745631679</v>
       </c>
       <c r="P96">
-        <v>3.676379789199999</v>
+        <v>3.640437021</v>
       </c>
       <c r="Q96">
-        <v>4.2363797892</v>
+        <v>4.200437021000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6236441637701999</v>
+        <v>0.7378099947459836</v>
       </c>
       <c r="T96">
-        <v>13.34513080300693</v>
+        <v>15.98175507496498</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9307,7 +9307,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.088130526612074</v>
+        <v>2.066150205279315</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9315,22 +9315,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09665879973729913</v>
+        <v>0.0967597896483863</v>
       </c>
       <c r="C97">
-        <v>0.8783434734785303</v>
+        <v>0.2877654946373269</v>
       </c>
       <c r="D97">
-        <v>34.25184347347853</v>
+        <v>34.23256549463733</v>
       </c>
       <c r="E97">
-        <v>51.9435</v>
+        <v>52.5148</v>
       </c>
       <c r="F97">
-        <v>54.2735</v>
+        <v>54.8448</v>
       </c>
       <c r="G97">
         <v>20.9</v>
@@ -9351,28 +9351,28 @@
         <v>8.5</v>
       </c>
       <c r="M97">
-        <v>4.1139313</v>
+        <v>4.15723584</v>
       </c>
       <c r="N97">
-        <v>4.3860687</v>
+        <v>4.34276416</v>
       </c>
       <c r="O97">
-        <v>0.745631679</v>
+        <v>0.7382699072</v>
       </c>
       <c r="P97">
-        <v>3.640437021</v>
+        <v>3.6044942528</v>
       </c>
       <c r="Q97">
-        <v>4.200437021000001</v>
+        <v>4.164494252800001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7378099947459836</v>
+        <v>0.9090587412096591</v>
       </c>
       <c r="T97">
-        <v>15.98175507496498</v>
+        <v>19.93669148290206</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9389,7 +9389,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.066150205279315</v>
+        <v>2.044627807307656</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9397,22 +9397,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.0967597896483863</v>
+        <v>0.09686077955947348</v>
       </c>
       <c r="C98">
-        <v>0.287765494637334</v>
+        <v>-0.3027907959454978</v>
       </c>
       <c r="D98">
-        <v>34.23256549463733</v>
+        <v>34.2133092040545</v>
       </c>
       <c r="E98">
-        <v>52.51479999999999</v>
+        <v>53.08609999999999</v>
       </c>
       <c r="F98">
-        <v>54.84479999999999</v>
+        <v>55.41609999999999</v>
       </c>
       <c r="G98">
         <v>20.9</v>
@@ -9433,28 +9433,28 @@
         <v>8.5</v>
       </c>
       <c r="M98">
-        <v>4.157235839999999</v>
+        <v>4.20054038</v>
       </c>
       <c r="N98">
-        <v>4.342764160000001</v>
+        <v>4.29945962</v>
       </c>
       <c r="O98">
-        <v>0.7382699072000002</v>
+        <v>0.7309081354000001</v>
       </c>
       <c r="P98">
-        <v>3.6044942528</v>
+        <v>3.5685514846</v>
       </c>
       <c r="Q98">
-        <v>4.164494252800001</v>
+        <v>4.128551484600001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9090587412096568</v>
+        <v>1.194473318649115</v>
       </c>
       <c r="T98">
-        <v>19.93669148290201</v>
+        <v>26.52825216279711</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9471,7 +9471,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.044627807307656</v>
+        <v>2.023549170118917</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9479,22 +9479,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09686077955947348</v>
+        <v>0.09696176947056065</v>
       </c>
       <c r="C99">
-        <v>-0.3027907959454978</v>
+        <v>-0.8933254348492383</v>
       </c>
       <c r="D99">
-        <v>34.2133092040545</v>
+        <v>34.19407456515076</v>
       </c>
       <c r="E99">
-        <v>53.08609999999999</v>
+        <v>53.6574</v>
       </c>
       <c r="F99">
-        <v>55.41609999999999</v>
+        <v>55.98739999999999</v>
       </c>
       <c r="G99">
         <v>20.9</v>
@@ -9515,28 +9515,28 @@
         <v>8.5</v>
       </c>
       <c r="M99">
-        <v>4.20054038</v>
+        <v>4.24384492</v>
       </c>
       <c r="N99">
-        <v>4.29945962</v>
+        <v>4.25615508</v>
       </c>
       <c r="O99">
-        <v>0.7309081354000001</v>
+        <v>0.7235463636</v>
       </c>
       <c r="P99">
-        <v>3.5685514846</v>
+        <v>3.5326087164</v>
       </c>
       <c r="Q99">
-        <v>4.128551484600001</v>
+        <v>4.092608716400001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.194473318649115</v>
+        <v>1.765302473528031</v>
       </c>
       <c r="T99">
-        <v>26.52825216279711</v>
+        <v>39.71137352258732</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.023549170118917</v>
+        <v>2.002900709199336</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9561,22 +9561,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09696176947056065</v>
+        <v>0.1087308993816478</v>
       </c>
       <c r="C100">
-        <v>-0.8933254348492383</v>
+        <v>-3.567172432791736</v>
       </c>
       <c r="D100">
-        <v>34.19407456515076</v>
+        <v>32.09152756720826</v>
       </c>
       <c r="E100">
-        <v>53.6574</v>
+        <v>54.2287</v>
       </c>
       <c r="F100">
-        <v>55.98739999999999</v>
+        <v>56.55869999999999</v>
       </c>
       <c r="G100">
         <v>20.9</v>
@@ -9597,129 +9597,47 @@
         <v>8.5</v>
       </c>
       <c r="M100">
-        <v>4.24384492</v>
+        <v>5.090282999999999</v>
       </c>
       <c r="N100">
-        <v>4.25615508</v>
+        <v>3.409717000000001</v>
       </c>
       <c r="O100">
-        <v>0.7235463636</v>
+        <v>0.5796518900000002</v>
       </c>
       <c r="P100">
-        <v>3.5326087164</v>
+        <v>2.83006511</v>
       </c>
       <c r="Q100">
-        <v>4.092608716400001</v>
+        <v>3.390065110000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.765302473528031</v>
+        <v>3.477789938164778</v>
       </c>
       <c r="T100">
-        <v>39.71137352258732</v>
+        <v>79.26073760195793</v>
       </c>
       <c r="U100">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V100">
         <v>0.17</v>
       </c>
       <c r="W100">
-        <v>0.062914</v>
+        <v>0.07469999999999999</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y100">
-        <v>2.002900709199336</v>
+        <v>1.669848218655034</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1087308993816478</v>
-      </c>
-      <c r="C101">
-        <v>-3.567172432791736</v>
-      </c>
-      <c r="D101">
-        <v>32.09152756720826</v>
-      </c>
-      <c r="E101">
-        <v>54.2287</v>
-      </c>
-      <c r="F101">
-        <v>56.55869999999999</v>
-      </c>
-      <c r="G101">
-        <v>20.9</v>
-      </c>
-      <c r="H101">
-        <v>54.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>9.06</v>
-      </c>
-      <c r="K101">
-        <v>0.5600000000000005</v>
-      </c>
-      <c r="L101">
-        <v>8.5</v>
-      </c>
-      <c r="M101">
-        <v>5.090282999999999</v>
-      </c>
-      <c r="N101">
-        <v>3.409717000000001</v>
-      </c>
-      <c r="O101">
-        <v>0.5796518900000002</v>
-      </c>
-      <c r="P101">
-        <v>2.83006511</v>
-      </c>
-      <c r="Q101">
-        <v>3.390065110000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.477789938164778</v>
-      </c>
-      <c r="T101">
-        <v>79.26073760195793</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.17</v>
-      </c>
-      <c r="W101">
-        <v>0.07469999999999999</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.669848218655034</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
